--- a/research/traditional_assets/database/data/finland/finland_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_retail_special_lines.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,13 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.09888437386782099</v>
+      </c>
+      <c r="C2">
+        <v>760.825156981731</v>
+      </c>
+      <c r="D2">
+        <v>741.2111569817309</v>
       </c>
       <c r="E2">
-        <v>-200</v>
+        <v>-191.114</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.886000000000001</v>
       </c>
       <c r="G2">
         <v>28.5</v>
@@ -1442,43 +1451,45 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.0953188</v>
       </c>
       <c r="N2">
-        <v>-13.53333333333333</v>
+        <v>-15.62865213333334</v>
       </c>
       <c r="O2">
-        <v>-2.706666666666667</v>
+        <v>-3.125730426666667</v>
       </c>
       <c r="P2">
-        <v>-10.82666666666667</v>
+        <v>-12.50292170666667</v>
       </c>
       <c r="Q2">
-        <v>33.37333333333333</v>
+        <v>31.69707829333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.09442463022332152</v>
+      </c>
+      <c r="T2">
+        <v>0.9997735757015447</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-1.291768425247111</v>
+      </c>
+      <c r="W2">
+        <v>0.5403989946732689</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-6.458842126235556</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1486,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09888437386782099</v>
+        <v>0.100784373867821</v>
       </c>
       <c r="C3">
-        <v>760.825156981731</v>
+        <v>726.3264037720508</v>
       </c>
       <c r="D3">
-        <v>741.2111569817309</v>
+        <v>715.5984037720508</v>
       </c>
       <c r="E3">
-        <v>-191.114</v>
+        <v>-182.228</v>
       </c>
       <c r="F3">
-        <v>8.886000000000001</v>
+        <v>17.772</v>
       </c>
       <c r="G3">
         <v>28.5</v>
@@ -1522,37 +1533,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M3">
-        <v>2.0953188</v>
+        <v>4.190637600000001</v>
       </c>
       <c r="N3">
-        <v>-15.62865213333334</v>
+        <v>-17.72397093333333</v>
       </c>
       <c r="O3">
-        <v>-3.125730426666667</v>
+        <v>-3.544794186666667</v>
       </c>
       <c r="P3">
-        <v>-12.50292170666667</v>
+        <v>-14.17917674666667</v>
       </c>
       <c r="Q3">
-        <v>31.69707829333333</v>
+        <v>30.02082325333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09442463022332152</v>
+        <v>0.09492079991947786</v>
       </c>
       <c r="T3">
-        <v>0.9997735757015447</v>
+        <v>1.009975346882173</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-1.291768425247111</v>
+        <v>-0.6458842126235557</v>
       </c>
       <c r="W3">
-        <v>0.5403989946732689</v>
+        <v>0.3880994973366345</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1560,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-6.458842126235556</v>
+        <v>-3.229421063117777</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1568,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.100784373867821</v>
+        <v>0.102684373867821</v>
       </c>
       <c r="C4">
-        <v>726.3264037720508</v>
+        <v>693.5386382304939</v>
       </c>
       <c r="D4">
-        <v>715.5984037720508</v>
+        <v>691.6966382304939</v>
       </c>
       <c r="E4">
-        <v>-182.228</v>
+        <v>-173.342</v>
       </c>
       <c r="F4">
-        <v>17.772</v>
+        <v>26.658</v>
       </c>
       <c r="G4">
         <v>28.5</v>
@@ -1604,37 +1615,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M4">
-        <v>4.190637600000001</v>
+        <v>6.285956400000001</v>
       </c>
       <c r="N4">
-        <v>-17.72397093333333</v>
+        <v>-19.81928973333333</v>
       </c>
       <c r="O4">
-        <v>-3.544794186666667</v>
+        <v>-3.963857946666667</v>
       </c>
       <c r="P4">
-        <v>-14.17917674666667</v>
+        <v>-15.85543178666667</v>
       </c>
       <c r="Q4">
-        <v>30.02082325333334</v>
+        <v>28.34456821333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09492079991947786</v>
+        <v>0.09542719991864776</v>
       </c>
       <c r="T4">
-        <v>1.009975346882173</v>
+        <v>1.02038746386034</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-0.6458842126235557</v>
+        <v>-0.4305894750823704</v>
       </c>
       <c r="W4">
-        <v>0.3880994973366345</v>
+        <v>0.337332998224423</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1642,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-3.229421063117777</v>
+        <v>-2.152947375411852</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1650,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.102684373867821</v>
+        <v>0.104584373867821</v>
       </c>
       <c r="C5">
-        <v>693.5386382304939</v>
+        <v>662.295955218219</v>
       </c>
       <c r="D5">
-        <v>691.6966382304939</v>
+        <v>669.339955218219</v>
       </c>
       <c r="E5">
-        <v>-173.342</v>
+        <v>-164.456</v>
       </c>
       <c r="F5">
-        <v>26.658</v>
+        <v>35.544</v>
       </c>
       <c r="G5">
         <v>28.5</v>
@@ -1686,37 +1697,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M5">
-        <v>6.285956400000001</v>
+        <v>8.381275200000001</v>
       </c>
       <c r="N5">
-        <v>-19.81928973333333</v>
+        <v>-21.91460853333334</v>
       </c>
       <c r="O5">
-        <v>-3.963857946666667</v>
+        <v>-4.382921706666667</v>
       </c>
       <c r="P5">
-        <v>-15.85543178666667</v>
+        <v>-17.53168682666667</v>
       </c>
       <c r="Q5">
-        <v>28.34456821333334</v>
+        <v>26.66831317333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09542719991864776</v>
+        <v>0.09594414991780034</v>
       </c>
       <c r="T5">
-        <v>1.02038746386034</v>
+        <v>1.031016499942218</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.4305894750823704</v>
+        <v>-0.3229421063117778</v>
       </c>
       <c r="W5">
-        <v>0.337332998224423</v>
+        <v>0.3119497486683173</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1724,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-2.152947375411852</v>
+        <v>-1.614710531558889</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1732,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.104584373867821</v>
+        <v>0.106484373867821</v>
       </c>
       <c r="C6">
-        <v>662.295955218219</v>
+        <v>632.4532272525546</v>
       </c>
       <c r="D6">
-        <v>669.339955218219</v>
+        <v>648.3832272525545</v>
       </c>
       <c r="E6">
-        <v>-164.456</v>
+        <v>-155.57</v>
       </c>
       <c r="F6">
-        <v>35.544</v>
+        <v>44.43000000000001</v>
       </c>
       <c r="G6">
         <v>28.5</v>
@@ -1768,37 +1779,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M6">
-        <v>8.381275200000001</v>
+        <v>10.476594</v>
       </c>
       <c r="N6">
-        <v>-21.91460853333334</v>
+        <v>-24.00992733333334</v>
       </c>
       <c r="O6">
-        <v>-4.382921706666667</v>
+        <v>-4.801985466666668</v>
       </c>
       <c r="P6">
-        <v>-17.53168682666667</v>
+        <v>-19.20794186666667</v>
       </c>
       <c r="Q6">
-        <v>26.66831317333333</v>
+        <v>24.99205813333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09594414991780034</v>
+        <v>0.09647198307482979</v>
       </c>
       <c r="T6">
-        <v>1.031016499942218</v>
+        <v>1.041869305204768</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.3229421063117778</v>
+        <v>-0.2583536850494222</v>
       </c>
       <c r="W6">
-        <v>0.3119497486683173</v>
+        <v>0.2967197989346538</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1806,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-1.614710531558889</v>
+        <v>-1.291768425247111</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1814,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.106484373867821</v>
+        <v>0.108384373867821</v>
       </c>
       <c r="C7">
-        <v>632.4532272525546</v>
+        <v>603.8829505610323</v>
       </c>
       <c r="D7">
-        <v>648.3832272525545</v>
+        <v>628.6989505610323</v>
       </c>
       <c r="E7">
-        <v>-155.57</v>
+        <v>-146.684</v>
       </c>
       <c r="F7">
-        <v>44.43000000000001</v>
+        <v>53.316</v>
       </c>
       <c r="G7">
         <v>28.5</v>
@@ -1850,37 +1861,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M7">
-        <v>10.476594</v>
+        <v>12.5719128</v>
       </c>
       <c r="N7">
-        <v>-24.00992733333334</v>
+        <v>-26.10524613333334</v>
       </c>
       <c r="O7">
-        <v>-4.801985466666668</v>
+        <v>-5.221049226666668</v>
       </c>
       <c r="P7">
-        <v>-19.20794186666667</v>
+        <v>-20.88419690666667</v>
       </c>
       <c r="Q7">
-        <v>24.99205813333333</v>
+        <v>23.31580309333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09647198307482979</v>
+        <v>0.09701104672456204</v>
       </c>
       <c r="T7">
-        <v>1.041869305204768</v>
+        <v>1.052953021217584</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.2583536850494222</v>
+        <v>-0.2152947375411852</v>
       </c>
       <c r="W7">
-        <v>0.2967197989346538</v>
+        <v>0.2865664991122114</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1888,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-1.291768425247111</v>
+        <v>-1.076473687705926</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1896,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.108384373867821</v>
+        <v>0.110284373867821</v>
       </c>
       <c r="C8">
-        <v>603.8829505610323</v>
+        <v>576.4726487121151</v>
       </c>
       <c r="D8">
-        <v>628.6989505610323</v>
+        <v>610.1746487121151</v>
       </c>
       <c r="E8">
-        <v>-146.684</v>
+        <v>-137.798</v>
       </c>
       <c r="F8">
-        <v>53.316</v>
+        <v>62.202</v>
       </c>
       <c r="G8">
         <v>28.5</v>
@@ -1932,37 +1943,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M8">
-        <v>12.5719128</v>
+        <v>14.6672316</v>
       </c>
       <c r="N8">
-        <v>-26.10524613333334</v>
+        <v>-28.20056493333334</v>
       </c>
       <c r="O8">
-        <v>-5.221049226666668</v>
+        <v>-5.640112986666668</v>
       </c>
       <c r="P8">
-        <v>-20.88419690666667</v>
+        <v>-22.56045194666667</v>
       </c>
       <c r="Q8">
-        <v>23.31580309333333</v>
+        <v>21.63954805333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09701104672456204</v>
+        <v>0.09756170314095516</v>
       </c>
       <c r="T8">
-        <v>1.052953021217584</v>
+        <v>1.064275096714548</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.2152947375411852</v>
+        <v>-0.184538346463873</v>
       </c>
       <c r="W8">
-        <v>0.2865664991122114</v>
+        <v>0.2793141420961813</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1970,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-1.076473687705926</v>
+        <v>-0.9226917323193651</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1978,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.110284373867821</v>
+        <v>0.112184373867821</v>
       </c>
       <c r="C9">
-        <v>576.472648712115</v>
+        <v>550.1227221130422</v>
       </c>
       <c r="D9">
-        <v>610.174648712115</v>
+        <v>592.7107221130422</v>
       </c>
       <c r="E9">
-        <v>-137.798</v>
+        <v>-128.912</v>
       </c>
       <c r="F9">
-        <v>62.20200000000001</v>
+        <v>71.08800000000001</v>
       </c>
       <c r="G9">
         <v>28.5</v>
@@ -2014,37 +2025,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M9">
-        <v>14.6672316</v>
+        <v>16.7625504</v>
       </c>
       <c r="N9">
-        <v>-28.20056493333334</v>
+        <v>-30.29588373333334</v>
       </c>
       <c r="O9">
-        <v>-5.640112986666669</v>
+        <v>-6.059176746666668</v>
       </c>
       <c r="P9">
-        <v>-22.56045194666667</v>
+        <v>-24.23670698666667</v>
       </c>
       <c r="Q9">
-        <v>21.63954805333333</v>
+        <v>19.96329301333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09756170314095516</v>
+        <v>0.09812433034900904</v>
       </c>
       <c r="T9">
-        <v>1.064275096714548</v>
+        <v>1.075843304287532</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.184538346463873</v>
+        <v>-0.1614710531558889</v>
       </c>
       <c r="W9">
-        <v>0.2793141420961813</v>
+        <v>0.2738748743341586</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2052,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.9226917323193651</v>
+        <v>-0.8073552657794445</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2060,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.112184373867821</v>
+        <v>0.114084373867821</v>
       </c>
       <c r="C10">
-        <v>550.1227221130422</v>
+        <v>524.7446565316151</v>
       </c>
       <c r="D10">
-        <v>592.7107221130422</v>
+        <v>576.2186565316151</v>
       </c>
       <c r="E10">
-        <v>-128.912</v>
+        <v>-120.026</v>
       </c>
       <c r="F10">
-        <v>71.08800000000001</v>
+        <v>79.974</v>
       </c>
       <c r="G10">
         <v>28.5</v>
@@ -2096,37 +2107,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M10">
-        <v>16.7625504</v>
+        <v>18.8578692</v>
       </c>
       <c r="N10">
-        <v>-30.29588373333334</v>
+        <v>-32.39120253333334</v>
       </c>
       <c r="O10">
-        <v>-6.059176746666668</v>
+        <v>-6.478240506666669</v>
       </c>
       <c r="P10">
-        <v>-24.23670698666667</v>
+        <v>-25.91296202666667</v>
       </c>
       <c r="Q10">
-        <v>19.96329301333333</v>
+        <v>18.28703797333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09812433034900904</v>
+        <v>0.09869932299020695</v>
       </c>
       <c r="T10">
-        <v>1.075843304287532</v>
+        <v>1.087665758180802</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.1614710531558889</v>
+        <v>-0.1435298250274568</v>
       </c>
       <c r="W10">
-        <v>0.2738748743341586</v>
+        <v>0.2696443327414743</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2134,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.8073552657794445</v>
+        <v>-0.7176491251372841</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2142,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.114084373867821</v>
+        <v>0.115984373867821</v>
       </c>
       <c r="C11">
-        <v>524.7446565316151</v>
+        <v>500.2595226065633</v>
       </c>
       <c r="D11">
-        <v>576.2186565316151</v>
+        <v>560.6195226065634</v>
       </c>
       <c r="E11">
-        <v>-120.026</v>
+        <v>-111.14</v>
       </c>
       <c r="F11">
-        <v>79.974</v>
+        <v>88.86</v>
       </c>
       <c r="G11">
         <v>28.5</v>
@@ -2178,37 +2189,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M11">
-        <v>18.8578692</v>
+        <v>20.953188</v>
       </c>
       <c r="N11">
-        <v>-32.39120253333334</v>
+        <v>-34.48652133333334</v>
       </c>
       <c r="O11">
-        <v>-6.478240506666669</v>
+        <v>-6.897304266666668</v>
       </c>
       <c r="P11">
-        <v>-25.91296202666667</v>
+        <v>-27.58921706666667</v>
       </c>
       <c r="Q11">
-        <v>18.28703797333333</v>
+        <v>16.61078293333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09869932299020695</v>
+        <v>0.09928709324565368</v>
       </c>
       <c r="T11">
-        <v>1.087665758180802</v>
+        <v>1.099750933271699</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.1435298250274568</v>
+        <v>-0.1291768425247111</v>
       </c>
       <c r="W11">
-        <v>0.2696443327414743</v>
+        <v>0.2662598994673269</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2216,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.7176491251372841</v>
+        <v>-0.6458842126235556</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2224,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.115984373867821</v>
+        <v>0.117884373867821</v>
       </c>
       <c r="C12">
-        <v>500.2595226065631</v>
+        <v>476.5967126573548</v>
       </c>
       <c r="D12">
-        <v>560.6195226065631</v>
+        <v>545.8427126573548</v>
       </c>
       <c r="E12">
-        <v>-111.14</v>
+        <v>-102.254</v>
       </c>
       <c r="F12">
-        <v>88.86000000000001</v>
+        <v>97.74600000000001</v>
       </c>
       <c r="G12">
         <v>28.5</v>
@@ -2260,37 +2271,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M12">
-        <v>20.953188</v>
+        <v>23.0485068</v>
       </c>
       <c r="N12">
-        <v>-34.48652133333334</v>
+        <v>-36.58184013333334</v>
       </c>
       <c r="O12">
-        <v>-6.897304266666669</v>
+        <v>-7.316368026666668</v>
       </c>
       <c r="P12">
-        <v>-27.58921706666667</v>
+        <v>-29.26547210666667</v>
       </c>
       <c r="Q12">
-        <v>16.61078293333333</v>
+        <v>14.93452789333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09928709324565368</v>
+        <v>0.09988807182144754</v>
       </c>
       <c r="T12">
-        <v>1.099750933271699</v>
+        <v>1.112107685330932</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.1291768425247111</v>
+        <v>-0.1174334932042829</v>
       </c>
       <c r="W12">
-        <v>0.2662598994673269</v>
+        <v>0.2634908176975699</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2298,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.6458842126235558</v>
+        <v>-0.5871674660214141</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2306,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.117884373867821</v>
+        <v>0.119784373867821</v>
       </c>
       <c r="C13">
-        <v>476.5967126573548</v>
+        <v>453.6928721346812</v>
       </c>
       <c r="D13">
-        <v>545.8427126573548</v>
+        <v>531.8248721346812</v>
       </c>
       <c r="E13">
-        <v>-102.254</v>
+        <v>-93.36799999999999</v>
       </c>
       <c r="F13">
-        <v>97.74600000000001</v>
+        <v>106.632</v>
       </c>
       <c r="G13">
         <v>28.5</v>
@@ -2342,37 +2353,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M13">
-        <v>23.0485068</v>
+        <v>25.1438256</v>
       </c>
       <c r="N13">
-        <v>-36.58184013333334</v>
+        <v>-38.67715893333334</v>
       </c>
       <c r="O13">
-        <v>-7.316368026666668</v>
+        <v>-7.735431786666668</v>
       </c>
       <c r="P13">
-        <v>-29.26547210666667</v>
+        <v>-30.94172714666667</v>
       </c>
       <c r="Q13">
-        <v>14.93452789333333</v>
+        <v>13.25827285333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09988807182144754</v>
+        <v>0.1005027090012367</v>
       </c>
       <c r="T13">
-        <v>1.112107685330932</v>
+        <v>1.124745272664238</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.1174334932042829</v>
+        <v>-0.1076473687705926</v>
       </c>
       <c r="W13">
-        <v>0.2634908176975699</v>
+        <v>0.2611832495561057</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2380,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.5871674660214141</v>
+        <v>-0.538236843852963</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2388,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.119784373867821</v>
+        <v>0.121684373867821</v>
       </c>
       <c r="C14">
-        <v>453.6928721346812</v>
+        <v>431.4909915975898</v>
       </c>
       <c r="D14">
-        <v>531.8248721346812</v>
+        <v>518.5089915975898</v>
       </c>
       <c r="E14">
-        <v>-93.36799999999999</v>
+        <v>-84.482</v>
       </c>
       <c r="F14">
-        <v>106.632</v>
+        <v>115.518</v>
       </c>
       <c r="G14">
         <v>28.5</v>
@@ -2424,37 +2435,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M14">
-        <v>25.1438256</v>
+        <v>27.2391444</v>
       </c>
       <c r="N14">
-        <v>-38.67715893333334</v>
+        <v>-40.77247773333333</v>
       </c>
       <c r="O14">
-        <v>-7.735431786666668</v>
+        <v>-8.154495546666666</v>
       </c>
       <c r="P14">
-        <v>-30.94172714666667</v>
+        <v>-32.61798218666667</v>
       </c>
       <c r="Q14">
-        <v>13.25827285333333</v>
+        <v>11.58201781333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1005027090012367</v>
+        <v>0.1011314757713659</v>
       </c>
       <c r="T14">
-        <v>1.124745272664238</v>
+        <v>1.137673379246586</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.1076473687705926</v>
+        <v>-0.09936680194208548</v>
       </c>
       <c r="W14">
-        <v>0.2611832495561057</v>
+        <v>0.2592306918979438</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2462,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.538236843852963</v>
+        <v>-0.4968340097104273</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2470,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.121684373867821</v>
+        <v>0.123584373867821</v>
       </c>
       <c r="C15">
-        <v>431.4909915975898</v>
+        <v>409.9396317695409</v>
       </c>
       <c r="D15">
-        <v>518.5089915975898</v>
+        <v>505.843631769541</v>
       </c>
       <c r="E15">
-        <v>-84.482</v>
+        <v>-75.59599999999999</v>
       </c>
       <c r="F15">
-        <v>115.518</v>
+        <v>124.404</v>
       </c>
       <c r="G15">
         <v>28.5</v>
@@ -2506,37 +2517,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M15">
-        <v>27.2391444</v>
+        <v>29.33446320000001</v>
       </c>
       <c r="N15">
-        <v>-40.77247773333333</v>
+        <v>-42.86779653333334</v>
       </c>
       <c r="O15">
-        <v>-8.154495546666666</v>
+        <v>-8.573559306666668</v>
       </c>
       <c r="P15">
-        <v>-32.61798218666667</v>
+        <v>-34.29423722666667</v>
       </c>
       <c r="Q15">
-        <v>11.58201781333334</v>
+        <v>9.905762773333329</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1011314757713659</v>
+        <v>0.1017748650245213</v>
       </c>
       <c r="T15">
-        <v>1.137673379246586</v>
+        <v>1.150902139470383</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.09936680194208548</v>
+        <v>-0.09226917323193651</v>
       </c>
       <c r="W15">
-        <v>0.2592306918979438</v>
+        <v>0.2575570710480906</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2544,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.4968340097104273</v>
+        <v>-0.4613458661596825</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2552,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.123584373867821</v>
+        <v>0.125484373867821</v>
       </c>
       <c r="C16">
-        <v>409.9396317695409</v>
+        <v>388.9922594613844</v>
       </c>
       <c r="D16">
-        <v>505.843631769541</v>
+        <v>493.7822594613844</v>
       </c>
       <c r="E16">
-        <v>-75.59599999999999</v>
+        <v>-66.70999999999998</v>
       </c>
       <c r="F16">
-        <v>124.404</v>
+        <v>133.29</v>
       </c>
       <c r="G16">
         <v>28.5</v>
@@ -2588,37 +2599,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M16">
-        <v>29.33446320000001</v>
+        <v>31.42978200000001</v>
       </c>
       <c r="N16">
-        <v>-42.86779653333334</v>
+        <v>-44.96311533333334</v>
       </c>
       <c r="O16">
-        <v>-8.573559306666668</v>
+        <v>-8.992623066666669</v>
       </c>
       <c r="P16">
-        <v>-34.29423722666667</v>
+        <v>-35.97049226666667</v>
       </c>
       <c r="Q16">
-        <v>9.905762773333329</v>
+        <v>8.229507733333328</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1017748650245213</v>
+        <v>0.1024333928483392</v>
       </c>
       <c r="T16">
-        <v>1.150902139470383</v>
+        <v>1.164442164640623</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.09226917323193651</v>
+        <v>-0.08611789501647407</v>
       </c>
       <c r="W16">
-        <v>0.2575570710480906</v>
+        <v>0.2561065996448846</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2626,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.4613458661596825</v>
+        <v>-0.4305894750823704</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2634,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.125484373867821</v>
+        <v>0.127384373867821</v>
       </c>
       <c r="C17">
-        <v>388.9922594613847</v>
+        <v>368.6066762875695</v>
       </c>
       <c r="D17">
-        <v>493.7822594613846</v>
+        <v>482.2826762875695</v>
       </c>
       <c r="E17">
-        <v>-66.71000000000001</v>
+        <v>-57.82399999999998</v>
       </c>
       <c r="F17">
-        <v>133.29</v>
+        <v>142.176</v>
       </c>
       <c r="G17">
         <v>28.5</v>
@@ -2670,37 +2681,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M17">
-        <v>31.429782</v>
+        <v>33.5251008</v>
       </c>
       <c r="N17">
-        <v>-44.96311533333333</v>
+        <v>-47.05843413333334</v>
       </c>
       <c r="O17">
-        <v>-8.992623066666667</v>
+        <v>-9.411686826666667</v>
       </c>
       <c r="P17">
-        <v>-35.97049226666667</v>
+        <v>-37.64674730666667</v>
       </c>
       <c r="Q17">
-        <v>8.229507733333335</v>
+        <v>6.553252693333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1024333928483392</v>
+        <v>0.1031075999060575</v>
       </c>
       <c r="T17">
-        <v>1.164442164640623</v>
+        <v>1.178304571362535</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.0861178950164741</v>
+        <v>-0.08073552657794446</v>
       </c>
       <c r="W17">
-        <v>0.2561065996448846</v>
+        <v>0.2548374371670793</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2708,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.4305894750823704</v>
+        <v>-0.403677632889722</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2716,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.127384373867821</v>
+        <v>0.129284373867821</v>
       </c>
       <c r="C18">
-        <v>368.6066762875695</v>
+        <v>348.7445253925865</v>
       </c>
       <c r="D18">
-        <v>482.2826762875695</v>
+        <v>471.3065253925865</v>
       </c>
       <c r="E18">
-        <v>-57.82399999999998</v>
+        <v>-48.93799999999999</v>
       </c>
       <c r="F18">
-        <v>142.176</v>
+        <v>151.062</v>
       </c>
       <c r="G18">
         <v>28.5</v>
@@ -2752,37 +2763,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M18">
-        <v>33.5251008</v>
+        <v>35.62041960000001</v>
       </c>
       <c r="N18">
-        <v>-47.05843413333334</v>
+        <v>-49.15375293333334</v>
       </c>
       <c r="O18">
-        <v>-9.411686826666667</v>
+        <v>-9.830750586666667</v>
       </c>
       <c r="P18">
-        <v>-37.64674730666667</v>
+        <v>-39.32300234666667</v>
       </c>
       <c r="Q18">
-        <v>6.553252693333334</v>
+        <v>4.876997653333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1031075999060575</v>
+        <v>0.1037980529169739</v>
       </c>
       <c r="T18">
-        <v>1.178304571362535</v>
+        <v>1.192501011981361</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.08073552657794446</v>
+        <v>-0.07598637795571242</v>
       </c>
       <c r="W18">
-        <v>0.2548374371670793</v>
+        <v>0.253717587921957</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2790,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.403677632889722</v>
+        <v>-0.379931889778562</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2798,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.129284373867821</v>
+        <v>0.131184373867821</v>
       </c>
       <c r="C19">
-        <v>348.7445253925865</v>
+        <v>329.3708640362806</v>
       </c>
       <c r="D19">
-        <v>471.3065253925865</v>
+        <v>460.8188640362807</v>
       </c>
       <c r="E19">
-        <v>-48.93799999999999</v>
+        <v>-40.05199999999996</v>
       </c>
       <c r="F19">
-        <v>151.062</v>
+        <v>159.948</v>
       </c>
       <c r="G19">
         <v>28.5</v>
@@ -2834,37 +2845,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M19">
-        <v>35.62041960000001</v>
+        <v>37.71573840000001</v>
       </c>
       <c r="N19">
-        <v>-49.15375293333334</v>
+        <v>-51.24907173333335</v>
       </c>
       <c r="O19">
-        <v>-9.830750586666667</v>
+        <v>-10.24981434666667</v>
       </c>
       <c r="P19">
-        <v>-39.32300234666667</v>
+        <v>-40.99925738666668</v>
       </c>
       <c r="Q19">
-        <v>4.876997653333333</v>
+        <v>3.200742613333318</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1037980529169739</v>
+        <v>0.1045053462452297</v>
       </c>
       <c r="T19">
-        <v>1.192501011981361</v>
+        <v>1.207043707249426</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.07598637795571242</v>
+        <v>-0.07176491251372839</v>
       </c>
       <c r="W19">
-        <v>0.253717587921957</v>
+        <v>0.2527221663707371</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2872,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.379931889778562</v>
+        <v>-0.3588245625686419</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2880,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.131184373867821</v>
+        <v>0.133084373867821</v>
       </c>
       <c r="C20">
-        <v>329.3708640362806</v>
+        <v>310.453792002759</v>
       </c>
       <c r="D20">
-        <v>460.8188640362807</v>
+        <v>450.787792002759</v>
       </c>
       <c r="E20">
-        <v>-40.05199999999999</v>
+        <v>-31.166</v>
       </c>
       <c r="F20">
-        <v>159.948</v>
+        <v>168.834</v>
       </c>
       <c r="G20">
         <v>28.5</v>
@@ -2916,37 +2927,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M20">
-        <v>37.71573840000001</v>
+        <v>39.8110572</v>
       </c>
       <c r="N20">
-        <v>-51.24907173333334</v>
+        <v>-53.34439053333334</v>
       </c>
       <c r="O20">
-        <v>-10.24981434666667</v>
+        <v>-10.66887810666667</v>
       </c>
       <c r="P20">
-        <v>-40.99925738666667</v>
+        <v>-42.67551242666667</v>
       </c>
       <c r="Q20">
-        <v>3.200742613333333</v>
+        <v>1.524487573333332</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1045053462452296</v>
+        <v>0.1052301036062819</v>
       </c>
       <c r="T20">
-        <v>1.207043707249426</v>
+        <v>1.221945481412999</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.07176491251372839</v>
+        <v>-0.06798781185511113</v>
       </c>
       <c r="W20">
-        <v>0.2527221663707371</v>
+        <v>0.2518315260354352</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2954,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.3588245625686419</v>
+        <v>-0.3399390592755558</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2962,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.133084373867821</v>
+        <v>0.134984373867821</v>
       </c>
       <c r="C21">
-        <v>310.453792002759</v>
+        <v>291.9641275079605</v>
       </c>
       <c r="D21">
-        <v>450.787792002759</v>
+        <v>441.1841275079605</v>
       </c>
       <c r="E21">
-        <v>-31.166</v>
+        <v>-22.27999999999997</v>
       </c>
       <c r="F21">
-        <v>168.834</v>
+        <v>177.72</v>
       </c>
       <c r="G21">
         <v>28.5</v>
@@ -2998,37 +3009,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M21">
-        <v>39.8110572</v>
+        <v>41.90637600000001</v>
       </c>
       <c r="N21">
-        <v>-53.34439053333334</v>
+        <v>-55.43970933333334</v>
       </c>
       <c r="O21">
-        <v>-10.66887810666667</v>
+        <v>-11.08794186666667</v>
       </c>
       <c r="P21">
-        <v>-42.67551242666667</v>
+        <v>-44.35176746666667</v>
       </c>
       <c r="Q21">
-        <v>1.524487573333332</v>
+        <v>-0.1517674666666693</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1052301036062819</v>
+        <v>0.1059729799013604</v>
       </c>
       <c r="T21">
-        <v>1.221945481412999</v>
+        <v>1.237219799930662</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.06798781185511113</v>
+        <v>-0.06458842126235556</v>
       </c>
       <c r="W21">
-        <v>0.2518315260354352</v>
+        <v>0.2510299497336634</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3036,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.3399390592755558</v>
+        <v>-0.3229421063117777</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3044,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.134984373867821</v>
+        <v>0.136884373867821</v>
       </c>
       <c r="C22">
-        <v>291.9641275079605</v>
+        <v>273.8751236702047</v>
       </c>
       <c r="D22">
-        <v>441.1841275079605</v>
+        <v>431.9811236702048</v>
       </c>
       <c r="E22">
-        <v>-22.27999999999997</v>
+        <v>-13.39399999999998</v>
       </c>
       <c r="F22">
-        <v>177.72</v>
+        <v>186.606</v>
       </c>
       <c r="G22">
         <v>28.5</v>
@@ -3080,37 +3091,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M22">
-        <v>41.90637600000001</v>
+        <v>44.00169480000001</v>
       </c>
       <c r="N22">
-        <v>-55.43970933333334</v>
+        <v>-57.53502813333334</v>
       </c>
       <c r="O22">
-        <v>-11.08794186666667</v>
+        <v>-11.50700562666667</v>
       </c>
       <c r="P22">
-        <v>-44.35176746666667</v>
+        <v>-46.02802250666667</v>
       </c>
       <c r="Q22">
-        <v>-0.1517674666666693</v>
+        <v>-1.82802250666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1059729799013604</v>
+        <v>0.106734663191251</v>
       </c>
       <c r="T22">
-        <v>1.237219799930662</v>
+        <v>1.252880810056366</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.06458842126235556</v>
+        <v>-0.06151278215462434</v>
       </c>
       <c r="W22">
-        <v>0.2510299497336634</v>
+        <v>0.2503047140320604</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3118,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.3229421063117777</v>
+        <v>-0.3075639107731216</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3126,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.136884373867821</v>
+        <v>0.138784373867821</v>
       </c>
       <c r="C23">
-        <v>273.8751236702048</v>
+        <v>256.162219741808</v>
       </c>
       <c r="D23">
-        <v>431.9811236702048</v>
+        <v>423.154219741808</v>
       </c>
       <c r="E23">
-        <v>-13.39400000000001</v>
+        <v>-4.507999999999981</v>
       </c>
       <c r="F23">
-        <v>186.606</v>
+        <v>195.492</v>
       </c>
       <c r="G23">
         <v>28.5</v>
@@ -3162,37 +3173,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M23">
-        <v>44.0016948</v>
+        <v>46.0970136</v>
       </c>
       <c r="N23">
-        <v>-57.53502813333334</v>
+        <v>-59.63034693333334</v>
       </c>
       <c r="O23">
-        <v>-11.50700562666667</v>
+        <v>-11.92606938666667</v>
       </c>
       <c r="P23">
-        <v>-46.02802250666667</v>
+        <v>-47.70427754666667</v>
       </c>
       <c r="Q23">
-        <v>-1.82802250666667</v>
+        <v>-3.504277546666671</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.106734663191251</v>
+        <v>0.1075158768219081</v>
       </c>
       <c r="T23">
-        <v>1.252880810056366</v>
+        <v>1.268943384544268</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.06151278215462435</v>
+        <v>-0.05871674660214143</v>
       </c>
       <c r="W23">
-        <v>0.2503047140320604</v>
+        <v>0.249645408848785</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3200,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.3075639107731218</v>
+        <v>-0.2935837330107072</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3208,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.138784373867821</v>
+        <v>0.140684373867821</v>
       </c>
       <c r="C24">
-        <v>256.162219741808</v>
+        <v>238.8028222292793</v>
       </c>
       <c r="D24">
-        <v>423.154219741808</v>
+        <v>414.6808222292793</v>
       </c>
       <c r="E24">
-        <v>-4.507999999999981</v>
+        <v>4.378000000000014</v>
       </c>
       <c r="F24">
-        <v>195.492</v>
+        <v>204.378</v>
       </c>
       <c r="G24">
         <v>28.5</v>
@@ -3244,37 +3255,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M24">
-        <v>46.0970136</v>
+        <v>48.19233240000001</v>
       </c>
       <c r="N24">
-        <v>-59.63034693333334</v>
+        <v>-61.72566573333334</v>
       </c>
       <c r="O24">
-        <v>-11.92606938666667</v>
+        <v>-12.34513314666667</v>
       </c>
       <c r="P24">
-        <v>-47.70427754666667</v>
+        <v>-49.38053258666667</v>
       </c>
       <c r="Q24">
-        <v>-3.504277546666671</v>
+        <v>-5.180532586666672</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1075158768219081</v>
+        <v>0.1083173817156991</v>
       </c>
       <c r="T24">
-        <v>1.268943384544268</v>
+        <v>1.285423168759129</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.05871674660214143</v>
+        <v>-0.05616384457596135</v>
       </c>
       <c r="W24">
-        <v>0.249645408848785</v>
+        <v>0.2490434345510117</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3282,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.2935837330107072</v>
+        <v>-0.2808192228798068</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3290,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.140684373867821</v>
+        <v>0.142584373867821</v>
       </c>
       <c r="C25">
-        <v>238.8028222292793</v>
+        <v>221.7761117948483</v>
       </c>
       <c r="D25">
-        <v>414.6808222292793</v>
+        <v>406.5401117948483</v>
       </c>
       <c r="E25">
-        <v>4.378000000000014</v>
+        <v>13.26400000000001</v>
       </c>
       <c r="F25">
-        <v>204.378</v>
+        <v>213.264</v>
       </c>
       <c r="G25">
         <v>28.5</v>
@@ -3326,37 +3337,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M25">
-        <v>48.19233240000001</v>
+        <v>50.28765120000001</v>
       </c>
       <c r="N25">
-        <v>-61.72566573333334</v>
+        <v>-63.82098453333334</v>
       </c>
       <c r="O25">
-        <v>-12.34513314666667</v>
+        <v>-12.76419690666667</v>
       </c>
       <c r="P25">
-        <v>-49.38053258666667</v>
+        <v>-51.05678762666668</v>
       </c>
       <c r="Q25">
-        <v>-5.180532586666672</v>
+        <v>-6.856787626666673</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1083173817156991</v>
+        <v>0.1091399788435373</v>
       </c>
       <c r="T25">
-        <v>1.285423168759129</v>
+        <v>1.30233663150596</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.05616384457596135</v>
+        <v>-0.05382368438529631</v>
       </c>
       <c r="W25">
-        <v>0.2490434345510117</v>
+        <v>0.2484916247780529</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3364,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.2808192228798068</v>
+        <v>-0.2691184219264815</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3372,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.142584373867821</v>
+        <v>0.144484373867821</v>
       </c>
       <c r="C26">
-        <v>221.7761117948483</v>
+        <v>205.0628724646905</v>
       </c>
       <c r="D26">
-        <v>406.5401117948483</v>
+        <v>398.7128724646905</v>
       </c>
       <c r="E26">
-        <v>13.26400000000001</v>
+        <v>22.15000000000001</v>
       </c>
       <c r="F26">
-        <v>213.264</v>
+        <v>222.15</v>
       </c>
       <c r="G26">
         <v>28.5</v>
@@ -3408,37 +3419,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M26">
-        <v>50.28765120000001</v>
+        <v>52.38297</v>
       </c>
       <c r="N26">
-        <v>-63.82098453333334</v>
+        <v>-65.91630333333333</v>
       </c>
       <c r="O26">
-        <v>-12.76419690666667</v>
+        <v>-13.18326066666667</v>
       </c>
       <c r="P26">
-        <v>-51.05678762666668</v>
+        <v>-52.73304266666666</v>
       </c>
       <c r="Q26">
-        <v>-6.856787626666673</v>
+        <v>-8.53304266666666</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1091399788435373</v>
+        <v>0.1099845118947844</v>
       </c>
       <c r="T26">
-        <v>1.30233663150596</v>
+        <v>1.319701119926039</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.05382368438529631</v>
+        <v>-0.05167073700988445</v>
       </c>
       <c r="W26">
-        <v>0.2484916247780529</v>
+        <v>0.2479839597869307</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3446,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.2691184219264815</v>
+        <v>-0.2583536850494221</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3454,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.144484373867821</v>
+        <v>0.146384373867821</v>
       </c>
       <c r="C27">
-        <v>205.0628724646905</v>
+        <v>188.6453401942962</v>
       </c>
       <c r="D27">
-        <v>398.7128724646905</v>
+        <v>391.1813401942962</v>
       </c>
       <c r="E27">
-        <v>22.15000000000001</v>
+        <v>31.036</v>
       </c>
       <c r="F27">
-        <v>222.15</v>
+        <v>231.036</v>
       </c>
       <c r="G27">
         <v>28.5</v>
@@ -3490,37 +3501,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M27">
-        <v>52.38297</v>
+        <v>54.4782888</v>
       </c>
       <c r="N27">
-        <v>-65.91630333333333</v>
+        <v>-68.01162213333333</v>
       </c>
       <c r="O27">
-        <v>-13.18326066666667</v>
+        <v>-13.60232442666667</v>
       </c>
       <c r="P27">
-        <v>-52.73304266666666</v>
+        <v>-54.40929770666666</v>
       </c>
       <c r="Q27">
-        <v>-8.53304266666666</v>
+        <v>-10.20929770666666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1099845118947844</v>
+        <v>0.1108518701636328</v>
       </c>
       <c r="T27">
-        <v>1.319701119926039</v>
+        <v>1.337534918843958</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.05167073700988445</v>
+        <v>-0.04968340097104274</v>
       </c>
       <c r="W27">
-        <v>0.2479839597869307</v>
+        <v>0.2475153459489719</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3528,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.2583536850494221</v>
+        <v>-0.2484170048552137</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3536,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.146384373867821</v>
+        <v>0.148284373867821</v>
       </c>
       <c r="C28">
-        <v>188.6453401942962</v>
+        <v>172.5070682788941</v>
       </c>
       <c r="D28">
-        <v>391.1813401942962</v>
+        <v>383.9290682788941</v>
       </c>
       <c r="E28">
-        <v>31.036</v>
+        <v>39.92200000000003</v>
       </c>
       <c r="F28">
-        <v>231.036</v>
+        <v>239.922</v>
       </c>
       <c r="G28">
         <v>28.5</v>
@@ -3572,37 +3583,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M28">
-        <v>54.4782888</v>
+        <v>56.57360760000001</v>
       </c>
       <c r="N28">
-        <v>-68.01162213333333</v>
+        <v>-70.10694093333335</v>
       </c>
       <c r="O28">
-        <v>-13.60232442666667</v>
+        <v>-14.02138818666667</v>
       </c>
       <c r="P28">
-        <v>-54.40929770666666</v>
+        <v>-56.08555274666668</v>
       </c>
       <c r="Q28">
-        <v>-10.20929770666666</v>
+        <v>-11.88555274666668</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1108518701636328</v>
+        <v>0.1117429916727237</v>
       </c>
       <c r="T28">
-        <v>1.337534918843958</v>
+        <v>1.355857314992506</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.04968340097104274</v>
+        <v>-0.04784327500915227</v>
       </c>
       <c r="W28">
-        <v>0.2475153459489719</v>
+        <v>0.2470814442471581</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3610,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.2484170048552137</v>
+        <v>-0.2392163750457614</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3618,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.148284373867821</v>
+        <v>0.150184373867821</v>
       </c>
       <c r="C29">
-        <v>172.5070682788941</v>
+        <v>156.6328074626381</v>
       </c>
       <c r="D29">
-        <v>383.9290682788941</v>
+        <v>376.9408074626381</v>
       </c>
       <c r="E29">
-        <v>39.92200000000003</v>
+        <v>48.80800000000002</v>
       </c>
       <c r="F29">
-        <v>239.922</v>
+        <v>248.808</v>
       </c>
       <c r="G29">
         <v>28.5</v>
@@ -3654,37 +3665,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M29">
-        <v>56.57360760000001</v>
+        <v>58.66892640000001</v>
       </c>
       <c r="N29">
-        <v>-70.10694093333335</v>
+        <v>-72.20225973333335</v>
       </c>
       <c r="O29">
-        <v>-14.02138818666667</v>
+        <v>-14.44045194666667</v>
       </c>
       <c r="P29">
-        <v>-56.08555274666668</v>
+        <v>-57.76180778666668</v>
       </c>
       <c r="Q29">
-        <v>-11.88555274666668</v>
+        <v>-13.56180778666668</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1117429916727237</v>
+        <v>0.1126588665570671</v>
       </c>
       <c r="T29">
-        <v>1.355857314992506</v>
+        <v>1.374688666589624</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.04784327500915227</v>
+        <v>-0.04613458661596825</v>
       </c>
       <c r="W29">
-        <v>0.2470814442471581</v>
+        <v>0.2466785355240453</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3692,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.2392163750457614</v>
+        <v>-0.2306729330798414</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3700,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.150184373867821</v>
+        <v>0.152084373867821</v>
       </c>
       <c r="C30">
-        <v>156.6328074626381</v>
+        <v>141.0083989072123</v>
       </c>
       <c r="D30">
-        <v>376.9408074626381</v>
+        <v>370.2023989072123</v>
       </c>
       <c r="E30">
-        <v>48.80800000000002</v>
+        <v>57.69400000000002</v>
       </c>
       <c r="F30">
-        <v>248.808</v>
+        <v>257.694</v>
       </c>
       <c r="G30">
         <v>28.5</v>
@@ -3736,37 +3747,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M30">
-        <v>58.66892640000001</v>
+        <v>60.7642452</v>
       </c>
       <c r="N30">
-        <v>-72.20225973333335</v>
+        <v>-74.29757853333334</v>
       </c>
       <c r="O30">
-        <v>-14.44045194666667</v>
+        <v>-14.85951570666667</v>
       </c>
       <c r="P30">
-        <v>-57.76180778666668</v>
+        <v>-59.43806282666667</v>
       </c>
       <c r="Q30">
-        <v>-13.56180778666668</v>
+        <v>-15.23806282666666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1126588665570671</v>
+        <v>0.1136005407339272</v>
       </c>
       <c r="T30">
-        <v>1.374688666589624</v>
+        <v>1.394050478795112</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.04613458661596825</v>
+        <v>-0.04454373880162453</v>
       </c>
       <c r="W30">
-        <v>0.2466785355240453</v>
+        <v>0.2463034136094231</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3774,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.2306729330798414</v>
+        <v>-0.2227186940081225</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3782,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.152084373867821</v>
+        <v>0.153984373867821</v>
       </c>
       <c r="C31">
-        <v>141.0083989072124</v>
+        <v>125.6206784389394</v>
       </c>
       <c r="D31">
-        <v>370.2023989072124</v>
+        <v>363.7006784389393</v>
       </c>
       <c r="E31">
-        <v>57.69400000000002</v>
+        <v>66.57999999999998</v>
       </c>
       <c r="F31">
-        <v>257.694</v>
+        <v>266.58</v>
       </c>
       <c r="G31">
         <v>28.5</v>
@@ -3818,37 +3829,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M31">
-        <v>60.7642452</v>
+        <v>62.859564</v>
       </c>
       <c r="N31">
-        <v>-74.29757853333334</v>
+        <v>-76.39289733333334</v>
       </c>
       <c r="O31">
-        <v>-14.85951570666667</v>
+        <v>-15.27857946666667</v>
       </c>
       <c r="P31">
-        <v>-59.43806282666667</v>
+        <v>-61.11431786666667</v>
       </c>
       <c r="Q31">
-        <v>-15.23806282666666</v>
+        <v>-16.91431786666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1136005407339272</v>
+        <v>0.114569119887269</v>
       </c>
       <c r="T31">
-        <v>1.394050478795112</v>
+        <v>1.413965485635042</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.04454373880162453</v>
+        <v>-0.04305894750823705</v>
       </c>
       <c r="W31">
-        <v>0.2463034136094231</v>
+        <v>0.2459532998224423</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3856,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.2227186940081225</v>
+        <v>-0.2152947375411853</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3864,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.153984373867821</v>
+        <v>0.155884373867821</v>
       </c>
       <c r="C32">
-        <v>125.6206784389394</v>
+        <v>110.4573907117664</v>
       </c>
       <c r="D32">
-        <v>363.7006784389393</v>
+        <v>357.4233907117664</v>
       </c>
       <c r="E32">
-        <v>66.57999999999998</v>
+        <v>75.46600000000001</v>
       </c>
       <c r="F32">
-        <v>266.58</v>
+        <v>275.466</v>
       </c>
       <c r="G32">
         <v>28.5</v>
@@ -3900,37 +3911,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M32">
-        <v>62.859564</v>
+        <v>64.95488280000001</v>
       </c>
       <c r="N32">
-        <v>-76.39289733333334</v>
+        <v>-78.48821613333334</v>
       </c>
       <c r="O32">
-        <v>-15.27857946666667</v>
+        <v>-15.69764322666667</v>
       </c>
       <c r="P32">
-        <v>-61.11431786666667</v>
+        <v>-62.79057290666667</v>
       </c>
       <c r="Q32">
-        <v>-16.91431786666666</v>
+        <v>-18.59057290666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.114569119887269</v>
+        <v>0.1155657737986787</v>
       </c>
       <c r="T32">
-        <v>1.413965485635042</v>
+        <v>1.434457739050043</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.04305894750823705</v>
+        <v>-0.04166994920151972</v>
       </c>
       <c r="W32">
-        <v>0.2459532998224423</v>
+        <v>0.2456257740217184</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3938,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.2152947375411853</v>
+        <v>-0.2083497460075985</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3946,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.155884373867821</v>
+        <v>0.157784373867821</v>
       </c>
       <c r="C33">
-        <v>110.4573907117664</v>
+        <v>95.50711210845043</v>
       </c>
       <c r="D33">
-        <v>357.4233907117664</v>
+        <v>351.3591121084505</v>
       </c>
       <c r="E33">
-        <v>75.46600000000001</v>
+        <v>84.35200000000003</v>
       </c>
       <c r="F33">
-        <v>275.466</v>
+        <v>284.352</v>
       </c>
       <c r="G33">
         <v>28.5</v>
@@ -3982,37 +3993,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M33">
-        <v>64.95488280000001</v>
+        <v>67.05020160000001</v>
       </c>
       <c r="N33">
-        <v>-78.48821613333334</v>
+        <v>-80.58353493333334</v>
       </c>
       <c r="O33">
-        <v>-15.69764322666667</v>
+        <v>-16.11670698666667</v>
       </c>
       <c r="P33">
-        <v>-62.79057290666667</v>
+        <v>-64.46682794666667</v>
       </c>
       <c r="Q33">
-        <v>-18.59057290666667</v>
+        <v>-20.26682794666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1155657737986787</v>
+        <v>0.116591741060424</v>
       </c>
       <c r="T33">
-        <v>1.434457739050043</v>
+        <v>1.455552705800778</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.04166994920151972</v>
+        <v>-0.04036776328897223</v>
       </c>
       <c r="W33">
-        <v>0.2456257740217184</v>
+        <v>0.2453187185835397</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4020,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.2083497460075985</v>
+        <v>-0.201838816444861</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4028,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.157784373867821</v>
+        <v>0.159684373867821</v>
       </c>
       <c r="C34">
-        <v>95.50711210845043</v>
+        <v>80.75918135945352</v>
       </c>
       <c r="D34">
-        <v>351.3591121084505</v>
+        <v>345.4971813594535</v>
       </c>
       <c r="E34">
-        <v>84.35200000000003</v>
+        <v>93.238</v>
       </c>
       <c r="F34">
-        <v>284.352</v>
+        <v>293.238</v>
       </c>
       <c r="G34">
         <v>28.5</v>
@@ -4064,37 +4075,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M34">
-        <v>67.05020160000001</v>
+        <v>69.14552040000001</v>
       </c>
       <c r="N34">
-        <v>-80.58353493333334</v>
+        <v>-82.67885373333334</v>
       </c>
       <c r="O34">
-        <v>-16.11670698666667</v>
+        <v>-16.53577074666667</v>
       </c>
       <c r="P34">
-        <v>-64.46682794666667</v>
+        <v>-66.14308298666667</v>
       </c>
       <c r="Q34">
-        <v>-20.26682794666667</v>
+        <v>-21.94308298666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.116591741060424</v>
+        <v>0.1176483342105796</v>
       </c>
       <c r="T34">
-        <v>1.455552705800778</v>
+        <v>1.477277373051537</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.04036776328897223</v>
+        <v>-0.03914449773476095</v>
       </c>
       <c r="W34">
-        <v>0.2453187185835397</v>
+        <v>0.2450302725658567</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4102,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.201838816444861</v>
+        <v>-0.1957224886738047</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4110,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.159684373867821</v>
+        <v>0.161584373867821</v>
       </c>
       <c r="C35">
-        <v>80.75918135945352</v>
+        <v>66.20363699302317</v>
       </c>
       <c r="D35">
-        <v>345.4971813594535</v>
+        <v>339.8276369930232</v>
       </c>
       <c r="E35">
-        <v>93.238</v>
+        <v>102.124</v>
       </c>
       <c r="F35">
-        <v>293.238</v>
+        <v>302.124</v>
       </c>
       <c r="G35">
         <v>28.5</v>
@@ -4146,37 +4157,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M35">
-        <v>69.14552040000001</v>
+        <v>71.24083920000001</v>
       </c>
       <c r="N35">
-        <v>-82.67885373333334</v>
+        <v>-84.77417253333334</v>
       </c>
       <c r="O35">
-        <v>-16.53577074666667</v>
+        <v>-16.95483450666667</v>
       </c>
       <c r="P35">
-        <v>-66.14308298666667</v>
+        <v>-67.81933802666667</v>
       </c>
       <c r="Q35">
-        <v>-21.94308298666667</v>
+        <v>-23.61933802666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1176483342105796</v>
+        <v>0.1187369453349823</v>
       </c>
       <c r="T35">
-        <v>1.477277373051537</v>
+        <v>1.499660363552317</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.03914449773476095</v>
+        <v>-0.03799318897785621</v>
       </c>
       <c r="W35">
-        <v>0.2450302725658567</v>
+        <v>0.2447587939609785</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4184,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.1957224886738047</v>
+        <v>-0.189965944889281</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4192,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.161584373867821</v>
+        <v>0.163484373867821</v>
       </c>
       <c r="C36">
-        <v>66.20363699302317</v>
+        <v>51.83116084444003</v>
       </c>
       <c r="D36">
-        <v>339.8276369930232</v>
+        <v>334.3411608444401</v>
       </c>
       <c r="E36">
-        <v>102.124</v>
+        <v>111.01</v>
       </c>
       <c r="F36">
-        <v>302.124</v>
+        <v>311.01</v>
       </c>
       <c r="G36">
         <v>28.5</v>
@@ -4228,37 +4239,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M36">
-        <v>71.24083920000001</v>
+        <v>73.33615800000001</v>
       </c>
       <c r="N36">
-        <v>-84.77417253333334</v>
+        <v>-86.86949133333334</v>
       </c>
       <c r="O36">
-        <v>-16.95483450666667</v>
+        <v>-17.37389826666667</v>
       </c>
       <c r="P36">
-        <v>-67.81933802666667</v>
+        <v>-69.49559306666667</v>
       </c>
       <c r="Q36">
-        <v>-23.61933802666667</v>
+        <v>-25.29559306666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1187369453349823</v>
+        <v>0.1198590521862897</v>
       </c>
       <c r="T36">
-        <v>1.499660363552317</v>
+        <v>1.522732061453122</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.03799318897785621</v>
+        <v>-0.03690766929277461</v>
       </c>
       <c r="W36">
-        <v>0.2447587939609785</v>
+        <v>0.2445028284192363</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4266,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.189965944889281</v>
+        <v>-0.184538346463873</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4274,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.163484373867821</v>
+        <v>0.165384373867821</v>
       </c>
       <c r="C37">
-        <v>51.83116084444003</v>
+        <v>37.63302695053687</v>
       </c>
       <c r="D37">
-        <v>334.3411608444401</v>
+        <v>329.0290269505369</v>
       </c>
       <c r="E37">
-        <v>111.01</v>
+        <v>119.8960000000001</v>
       </c>
       <c r="F37">
-        <v>311.01</v>
+        <v>319.8960000000001</v>
       </c>
       <c r="G37">
         <v>28.5</v>
@@ -4310,37 +4321,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M37">
-        <v>73.33615800000001</v>
+        <v>75.43147680000003</v>
       </c>
       <c r="N37">
-        <v>-86.86949133333334</v>
+        <v>-88.96481013333336</v>
       </c>
       <c r="O37">
-        <v>-17.37389826666667</v>
+        <v>-17.79296202666667</v>
       </c>
       <c r="P37">
-        <v>-69.49559306666667</v>
+        <v>-71.17184810666669</v>
       </c>
       <c r="Q37">
-        <v>-25.29559306666667</v>
+        <v>-26.97184810666668</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1198590521862897</v>
+        <v>0.1210162248767005</v>
       </c>
       <c r="T37">
-        <v>1.522732061453122</v>
+        <v>1.546524749913327</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.03690766929277461</v>
+        <v>-0.0358824562568642</v>
       </c>
       <c r="W37">
-        <v>0.2445028284192363</v>
+        <v>0.2442610831853686</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4348,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.184538346463873</v>
+        <v>-0.1794122812843209</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4356,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.165384373867821</v>
+        <v>0.167284373867821</v>
       </c>
       <c r="C38">
-        <v>37.63302695053693</v>
+        <v>23.60105523991831</v>
       </c>
       <c r="D38">
-        <v>329.0290269505369</v>
+        <v>323.8830552399183</v>
       </c>
       <c r="E38">
-        <v>119.896</v>
+        <v>128.782</v>
       </c>
       <c r="F38">
-        <v>319.896</v>
+        <v>328.782</v>
       </c>
       <c r="G38">
         <v>28.5</v>
@@ -4392,37 +4403,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M38">
-        <v>75.43147680000001</v>
+        <v>77.5267956</v>
       </c>
       <c r="N38">
-        <v>-88.96481013333334</v>
+        <v>-91.06012893333333</v>
       </c>
       <c r="O38">
-        <v>-17.79296202666667</v>
+        <v>-18.21202578666667</v>
       </c>
       <c r="P38">
-        <v>-71.17184810666667</v>
+        <v>-72.84810314666666</v>
       </c>
       <c r="Q38">
-        <v>-26.97184810666667</v>
+        <v>-28.64810314666666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1210162248767005</v>
+        <v>0.1222101332080767</v>
       </c>
       <c r="T38">
-        <v>1.546524749913327</v>
+        <v>1.571072761816713</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.0358824562568642</v>
+        <v>-0.03491266014181382</v>
       </c>
       <c r="W38">
-        <v>0.2442610831853686</v>
+        <v>0.2440324052614397</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4430,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.1794122812843209</v>
+        <v>-0.174563300709069</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4438,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.167284373867821</v>
+        <v>0.169184373867821</v>
       </c>
       <c r="C39">
-        <v>23.60105523991831</v>
+        <v>9.727569501934227</v>
       </c>
       <c r="D39">
-        <v>323.8830552399183</v>
+        <v>318.8955695019342</v>
       </c>
       <c r="E39">
-        <v>128.782</v>
+        <v>137.668</v>
       </c>
       <c r="F39">
-        <v>328.782</v>
+        <v>337.668</v>
       </c>
       <c r="G39">
         <v>28.5</v>
@@ -4474,37 +4485,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M39">
-        <v>77.5267956</v>
+        <v>79.6221144</v>
       </c>
       <c r="N39">
-        <v>-91.06012893333333</v>
+        <v>-93.15544773333333</v>
       </c>
       <c r="O39">
-        <v>-18.21202578666667</v>
+        <v>-18.63108954666667</v>
       </c>
       <c r="P39">
-        <v>-72.84810314666666</v>
+        <v>-74.52435818666666</v>
       </c>
       <c r="Q39">
-        <v>-28.64810314666666</v>
+        <v>-30.32435818666666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1222101332080767</v>
+        <v>0.1234425547114328</v>
       </c>
       <c r="T39">
-        <v>1.571072761816713</v>
+        <v>1.596412645071821</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.03491266014181382</v>
+        <v>-0.03399390592755556</v>
       </c>
       <c r="W39">
-        <v>0.2440324052614397</v>
+        <v>0.2438157630177176</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4512,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.174563300709069</v>
+        <v>-0.1699695296377777</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4520,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.169184373867821</v>
+        <v>0.171084373867821</v>
       </c>
       <c r="C40">
-        <v>9.727569501934227</v>
+        <v>-3.994640819816823</v>
       </c>
       <c r="D40">
-        <v>318.8955695019342</v>
+        <v>314.0593591801832</v>
       </c>
       <c r="E40">
-        <v>137.668</v>
+        <v>146.554</v>
       </c>
       <c r="F40">
-        <v>337.668</v>
+        <v>346.554</v>
       </c>
       <c r="G40">
         <v>28.5</v>
@@ -4556,37 +4567,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M40">
-        <v>79.6221144</v>
+        <v>81.71743320000002</v>
       </c>
       <c r="N40">
-        <v>-93.15544773333333</v>
+        <v>-95.25076653333335</v>
       </c>
       <c r="O40">
-        <v>-18.63108954666667</v>
+        <v>-19.05015330666667</v>
       </c>
       <c r="P40">
-        <v>-74.52435818666666</v>
+        <v>-76.20061322666668</v>
       </c>
       <c r="Q40">
-        <v>-30.32435818666666</v>
+        <v>-32.00061322666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1234425547114328</v>
+        <v>0.124715383477194</v>
       </c>
       <c r="T40">
-        <v>1.596412645071821</v>
+        <v>1.62258334417136</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.03399390592755556</v>
+        <v>-0.03312226731402849</v>
       </c>
       <c r="W40">
-        <v>0.2438157630177176</v>
+        <v>0.2436102306326479</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4594,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.1699695296377777</v>
+        <v>-0.1656113365701424</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4602,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.171084373867821</v>
+        <v>0.172984373867821</v>
       </c>
       <c r="C41">
-        <v>-3.994640819816823</v>
+        <v>-17.57235540939763</v>
       </c>
       <c r="D41">
-        <v>314.0593591801832</v>
+        <v>309.3676445906024</v>
       </c>
       <c r="E41">
-        <v>146.554</v>
+        <v>155.4400000000001</v>
       </c>
       <c r="F41">
-        <v>346.554</v>
+        <v>355.4400000000001</v>
       </c>
       <c r="G41">
         <v>28.5</v>
@@ -4638,37 +4649,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M41">
-        <v>81.71743320000002</v>
+        <v>83.81275200000002</v>
       </c>
       <c r="N41">
-        <v>-95.25076653333335</v>
+        <v>-97.34608533333335</v>
       </c>
       <c r="O41">
-        <v>-19.05015330666667</v>
+        <v>-19.46921706666667</v>
       </c>
       <c r="P41">
-        <v>-76.20061322666668</v>
+        <v>-77.87686826666668</v>
       </c>
       <c r="Q41">
-        <v>-32.00061322666667</v>
+        <v>-33.67686826666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.124715383477194</v>
+        <v>0.1260306398684805</v>
       </c>
       <c r="T41">
-        <v>1.62258334417136</v>
+        <v>1.649626399907549</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.03312226731402849</v>
+        <v>-0.03229421063117778</v>
       </c>
       <c r="W41">
-        <v>0.2436102306326479</v>
+        <v>0.2434149748668318</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4676,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.1656113365701424</v>
+        <v>-0.1614710531558889</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4684,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.172984373867821</v>
+        <v>0.174884373867821</v>
       </c>
       <c r="C42">
-        <v>-17.57235540939763</v>
+        <v>-31.01195478869988</v>
       </c>
       <c r="D42">
-        <v>309.3676445906024</v>
+        <v>304.8140452113001</v>
       </c>
       <c r="E42">
-        <v>155.4400000000001</v>
+        <v>164.326</v>
       </c>
       <c r="F42">
-        <v>355.4400000000001</v>
+        <v>364.326</v>
       </c>
       <c r="G42">
         <v>28.5</v>
@@ -4720,37 +4731,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M42">
-        <v>83.81275200000002</v>
+        <v>85.9080708</v>
       </c>
       <c r="N42">
-        <v>-97.34608533333335</v>
+        <v>-99.44140413333334</v>
       </c>
       <c r="O42">
-        <v>-19.46921706666667</v>
+        <v>-19.88828082666667</v>
       </c>
       <c r="P42">
-        <v>-77.87686826666668</v>
+        <v>-79.55312330666666</v>
       </c>
       <c r="Q42">
-        <v>-33.67686826666667</v>
+        <v>-35.35312330666666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1260306398684805</v>
+        <v>0.1273904812221836</v>
       </c>
       <c r="T42">
-        <v>1.649626399907549</v>
+        <v>1.677586169397507</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.03229421063117778</v>
+        <v>-0.03150654695724662</v>
       </c>
       <c r="W42">
-        <v>0.2434149748668318</v>
+        <v>0.2432292437725188</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4758,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.1614710531558889</v>
+        <v>-0.157532734786233</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4766,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.174884373867821</v>
+        <v>0.176784373867821</v>
       </c>
       <c r="C43">
-        <v>-31.01195478869988</v>
+        <v>-44.31944926777345</v>
       </c>
       <c r="D43">
-        <v>304.8140452113001</v>
+        <v>300.3925507322266</v>
       </c>
       <c r="E43">
-        <v>164.326</v>
+        <v>173.212</v>
       </c>
       <c r="F43">
-        <v>364.326</v>
+        <v>373.212</v>
       </c>
       <c r="G43">
         <v>28.5</v>
@@ -4802,37 +4813,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M43">
-        <v>85.9080708</v>
+        <v>88.00338960000002</v>
       </c>
       <c r="N43">
-        <v>-99.44140413333334</v>
+        <v>-101.5367229333334</v>
       </c>
       <c r="O43">
-        <v>-19.88828082666667</v>
+        <v>-20.30734458666667</v>
       </c>
       <c r="P43">
-        <v>-79.55312330666666</v>
+        <v>-81.22937834666668</v>
       </c>
       <c r="Q43">
-        <v>-35.35312330666666</v>
+        <v>-37.02937834666668</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1273904812221836</v>
+        <v>0.1287972136570488</v>
       </c>
       <c r="T43">
-        <v>1.677586169397507</v>
+        <v>1.706510068869878</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.03150654695724662</v>
+        <v>-0.03075639107731217</v>
       </c>
       <c r="W43">
-        <v>0.2432292437725188</v>
+        <v>0.2430523570160302</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4840,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.157532734786233</v>
+        <v>-0.1537819553865607</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4848,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.176784373867821</v>
+        <v>0.178684373867821</v>
       </c>
       <c r="C44">
-        <v>-44.31944926777334</v>
+        <v>-57.50050541153746</v>
       </c>
       <c r="D44">
-        <v>300.3925507322267</v>
+        <v>296.0974945884626</v>
       </c>
       <c r="E44">
-        <v>173.212</v>
+        <v>182.098</v>
       </c>
       <c r="F44">
-        <v>373.212</v>
+        <v>382.098</v>
       </c>
       <c r="G44">
         <v>28.5</v>
@@ -4884,37 +4895,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M44">
-        <v>88.00338960000001</v>
+        <v>90.09870840000001</v>
       </c>
       <c r="N44">
-        <v>-101.5367229333333</v>
+        <v>-103.6320417333333</v>
       </c>
       <c r="O44">
-        <v>-20.30734458666667</v>
+        <v>-20.72640834666667</v>
       </c>
       <c r="P44">
-        <v>-81.22937834666666</v>
+        <v>-82.90563338666666</v>
       </c>
       <c r="Q44">
-        <v>-37.02937834666666</v>
+        <v>-38.70563338666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1287972136570488</v>
+        <v>0.1302533051247163</v>
       </c>
       <c r="T44">
-        <v>1.706510068869878</v>
+        <v>1.736448842007946</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.03075639107731218</v>
+        <v>-0.03004112616853747</v>
       </c>
       <c r="W44">
-        <v>0.2430523570160302</v>
+        <v>0.2428836975505411</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4922,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.1537819553865609</v>
+        <v>-0.1502056308426873</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4930,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.178684373867821</v>
+        <v>0.180584373867821</v>
       </c>
       <c r="C45">
-        <v>-57.50050541153746</v>
+        <v>-70.5604702679517</v>
       </c>
       <c r="D45">
-        <v>296.0974945884626</v>
+        <v>291.9235297320483</v>
       </c>
       <c r="E45">
-        <v>182.098</v>
+        <v>190.984</v>
       </c>
       <c r="F45">
-        <v>382.098</v>
+        <v>390.984</v>
       </c>
       <c r="G45">
         <v>28.5</v>
@@ -4966,37 +4977,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M45">
-        <v>90.09870840000001</v>
+        <v>92.19402720000001</v>
       </c>
       <c r="N45">
-        <v>-103.6320417333333</v>
+        <v>-105.7273605333333</v>
       </c>
       <c r="O45">
-        <v>-20.72640834666667</v>
+        <v>-21.14547210666667</v>
       </c>
       <c r="P45">
-        <v>-82.90563338666666</v>
+        <v>-84.58188842666667</v>
       </c>
       <c r="Q45">
-        <v>-38.70563338666666</v>
+        <v>-40.38188842666666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1302533051247163</v>
+        <v>0.1317613998590863</v>
       </c>
       <c r="T45">
-        <v>1.736448842007946</v>
+        <v>1.767456857043803</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.03004112616853747</v>
+        <v>-0.02935837330107071</v>
       </c>
       <c r="W45">
-        <v>0.2428836975505411</v>
+        <v>0.2427227044243925</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5004,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.1502056308426873</v>
+        <v>-0.1467918665053536</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5012,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.180584373867821</v>
+        <v>0.182484373867821</v>
       </c>
       <c r="C46">
-        <v>-70.5604702679517</v>
+        <v>-83.50439357546355</v>
       </c>
       <c r="D46">
-        <v>291.9235297320483</v>
+        <v>287.8656064245365</v>
       </c>
       <c r="E46">
-        <v>190.984</v>
+        <v>199.87</v>
       </c>
       <c r="F46">
-        <v>390.984</v>
+        <v>399.87</v>
       </c>
       <c r="G46">
         <v>28.5</v>
@@ -5048,37 +5059,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M46">
-        <v>92.19402720000001</v>
+        <v>94.28934600000001</v>
       </c>
       <c r="N46">
-        <v>-105.7273605333333</v>
+        <v>-107.8226793333333</v>
       </c>
       <c r="O46">
-        <v>-21.14547210666667</v>
+        <v>-21.56453586666667</v>
       </c>
       <c r="P46">
-        <v>-84.58188842666667</v>
+        <v>-86.25814346666667</v>
       </c>
       <c r="Q46">
-        <v>-40.38188842666666</v>
+        <v>-42.05814346666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1317613998590863</v>
+        <v>0.1333243344019787</v>
       </c>
       <c r="T46">
-        <v>1.767456857043803</v>
+        <v>1.799592436262781</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.02935837330107071</v>
+        <v>-0.02870596500549136</v>
       </c>
       <c r="W46">
-        <v>0.2427227044243925</v>
+        <v>0.2425688665482948</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5086,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.1467918665053536</v>
+        <v>-0.1435298250274568</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5094,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.182484373867821</v>
+        <v>0.184384373867821</v>
       </c>
       <c r="C47">
-        <v>-83.50439357546355</v>
+        <v>-96.33704814366394</v>
       </c>
       <c r="D47">
-        <v>287.8656064245365</v>
+        <v>283.9189518563361</v>
       </c>
       <c r="E47">
-        <v>199.87</v>
+        <v>208.756</v>
       </c>
       <c r="F47">
-        <v>399.87</v>
+        <v>408.756</v>
       </c>
       <c r="G47">
         <v>28.5</v>
@@ -5130,37 +5141,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M47">
-        <v>94.28934600000001</v>
+        <v>96.38466480000001</v>
       </c>
       <c r="N47">
-        <v>-107.8226793333333</v>
+        <v>-109.9179981333333</v>
       </c>
       <c r="O47">
-        <v>-21.56453586666667</v>
+        <v>-21.98359962666667</v>
       </c>
       <c r="P47">
-        <v>-86.25814346666667</v>
+        <v>-87.93439850666667</v>
       </c>
       <c r="Q47">
-        <v>-42.05814346666666</v>
+        <v>-43.73439850666666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1333243344019787</v>
+        <v>0.1349451554094228</v>
       </c>
       <c r="T47">
-        <v>1.799592436262781</v>
+        <v>1.832918222119499</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.02870596500549136</v>
+        <v>-0.02808192228798068</v>
       </c>
       <c r="W47">
-        <v>0.2425688665482948</v>
+        <v>0.2424217172755058</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5168,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.1435298250274568</v>
+        <v>-0.1404096114399034</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5176,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.184384373867821</v>
+        <v>0.186284373867821</v>
       </c>
       <c r="C48">
-        <v>-96.33704814366394</v>
+        <v>-109.0629485800968</v>
       </c>
       <c r="D48">
-        <v>283.9189518563361</v>
+        <v>280.0790514199032</v>
       </c>
       <c r="E48">
-        <v>208.756</v>
+        <v>217.6420000000001</v>
       </c>
       <c r="F48">
-        <v>408.756</v>
+        <v>417.6420000000001</v>
       </c>
       <c r="G48">
         <v>28.5</v>
@@ -5212,37 +5223,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M48">
-        <v>96.38466480000001</v>
+        <v>98.47998360000001</v>
       </c>
       <c r="N48">
-        <v>-109.9179981333333</v>
+        <v>-112.0133169333333</v>
       </c>
       <c r="O48">
-        <v>-21.98359962666667</v>
+        <v>-22.40266338666667</v>
       </c>
       <c r="P48">
-        <v>-87.93439850666667</v>
+        <v>-89.61065354666667</v>
       </c>
       <c r="Q48">
-        <v>-43.73439850666666</v>
+        <v>-45.41065354666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1349451554094228</v>
+        <v>0.1366271394737515</v>
       </c>
       <c r="T48">
-        <v>1.832918222119499</v>
+        <v>1.867501584800999</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.02808192228798068</v>
+        <v>-0.02748443457972577</v>
       </c>
       <c r="W48">
-        <v>0.2424217172755058</v>
+        <v>0.2422808296738994</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5250,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.1404096114399034</v>
+        <v>-0.1374221728986289</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5258,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.186284373867821</v>
+        <v>0.188184373867821</v>
       </c>
       <c r="C49">
-        <v>-109.0629485800968</v>
+        <v>-121.6863685177075</v>
       </c>
       <c r="D49">
-        <v>280.0790514199032</v>
+        <v>276.3416314822925</v>
       </c>
       <c r="E49">
-        <v>217.6420000000001</v>
+        <v>226.528</v>
       </c>
       <c r="F49">
-        <v>417.6420000000001</v>
+        <v>426.528</v>
       </c>
       <c r="G49">
         <v>28.5</v>
@@ -5294,37 +5305,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M49">
-        <v>98.47998360000001</v>
+        <v>100.5753024</v>
       </c>
       <c r="N49">
-        <v>-112.0133169333333</v>
+        <v>-114.1086357333333</v>
       </c>
       <c r="O49">
-        <v>-22.40266338666667</v>
+        <v>-22.82172714666667</v>
       </c>
       <c r="P49">
-        <v>-89.61065354666667</v>
+        <v>-91.28690858666667</v>
       </c>
       <c r="Q49">
-        <v>-45.41065354666667</v>
+        <v>-47.08690858666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1366271394737515</v>
+        <v>0.1383738152328621</v>
       </c>
       <c r="T49">
-        <v>1.867501584800999</v>
+        <v>1.903415076816402</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.02748443457972577</v>
+        <v>-0.02691184219264815</v>
       </c>
       <c r="W49">
-        <v>0.2422808296738994</v>
+        <v>0.2421458123890265</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5332,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.1374221728986289</v>
+        <v>-0.1345592109632407</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5340,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.188184373867821</v>
+        <v>0.190084373867821</v>
       </c>
       <c r="C50">
-        <v>-121.6863685177074</v>
+        <v>-134.2113564811397</v>
       </c>
       <c r="D50">
-        <v>276.3416314822926</v>
+        <v>272.7026435188603</v>
       </c>
       <c r="E50">
-        <v>226.528</v>
+        <v>235.414</v>
       </c>
       <c r="F50">
-        <v>426.528</v>
+        <v>435.414</v>
       </c>
       <c r="G50">
         <v>28.5</v>
@@ -5376,37 +5387,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M50">
-        <v>100.5753024</v>
+        <v>102.6706212</v>
       </c>
       <c r="N50">
-        <v>-114.1086357333333</v>
+        <v>-116.2039545333333</v>
       </c>
       <c r="O50">
-        <v>-22.82172714666667</v>
+        <v>-23.24079090666667</v>
       </c>
       <c r="P50">
-        <v>-91.28690858666667</v>
+        <v>-92.96316362666667</v>
       </c>
       <c r="Q50">
-        <v>-47.08690858666667</v>
+        <v>-48.76316362666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1383738152328621</v>
+        <v>0.1401889880805653</v>
       </c>
       <c r="T50">
-        <v>1.903415076816402</v>
+        <v>1.940736941067704</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.02691184219264815</v>
+        <v>-0.02636262092341043</v>
       </c>
       <c r="W50">
-        <v>0.2421458123890265</v>
+        <v>0.2420163060137402</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5414,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.1345592109632407</v>
+        <v>-0.1318131046170521</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5422,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.190084373867821</v>
+        <v>0.191984373867821</v>
       </c>
       <c r="C51">
-        <v>-134.2113564811397</v>
+        <v>-146.6417505157191</v>
       </c>
       <c r="D51">
-        <v>272.7026435188603</v>
+        <v>269.1582494842809</v>
       </c>
       <c r="E51">
-        <v>235.414</v>
+        <v>244.3</v>
       </c>
       <c r="F51">
-        <v>435.414</v>
+        <v>444.3</v>
       </c>
       <c r="G51">
         <v>28.5</v>
@@ -5458,37 +5469,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M51">
-        <v>102.6706212</v>
+        <v>104.76594</v>
       </c>
       <c r="N51">
-        <v>-116.2039545333333</v>
+        <v>-118.2992733333333</v>
       </c>
       <c r="O51">
-        <v>-23.24079090666667</v>
+        <v>-23.65985466666667</v>
       </c>
       <c r="P51">
-        <v>-92.96316362666667</v>
+        <v>-94.63941866666667</v>
       </c>
       <c r="Q51">
-        <v>-48.76316362666667</v>
+        <v>-50.43941866666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1401889880805653</v>
+        <v>0.1420767678421766</v>
       </c>
       <c r="T51">
-        <v>1.940736941067704</v>
+        <v>1.979551679889058</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.02636262092341043</v>
+        <v>-0.02583536850494222</v>
       </c>
       <c r="W51">
-        <v>0.2420163060137402</v>
+        <v>0.2418919798934654</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5496,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.1318131046170521</v>
+        <v>-0.1291768425247111</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5504,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.191984373867821</v>
+        <v>0.193884373867821</v>
       </c>
       <c r="C52">
-        <v>-146.6417505157191</v>
+        <v>-158.9811916902526</v>
       </c>
       <c r="D52">
-        <v>269.1582494842809</v>
+        <v>265.7048083097474</v>
       </c>
       <c r="E52">
-        <v>244.3</v>
+        <v>253.186</v>
       </c>
       <c r="F52">
-        <v>444.3</v>
+        <v>453.186</v>
       </c>
       <c r="G52">
         <v>28.5</v>
@@ -5540,37 +5551,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M52">
-        <v>104.76594</v>
+        <v>106.8612588</v>
       </c>
       <c r="N52">
-        <v>-118.2992733333333</v>
+        <v>-120.3945921333333</v>
       </c>
       <c r="O52">
-        <v>-23.65985466666667</v>
+        <v>-24.07891842666667</v>
       </c>
       <c r="P52">
-        <v>-94.63941866666667</v>
+        <v>-96.31567370666667</v>
       </c>
       <c r="Q52">
-        <v>-50.43941866666667</v>
+        <v>-52.11567370666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1420767678421766</v>
+        <v>0.1440415998389558</v>
       </c>
       <c r="T52">
-        <v>1.979551679889058</v>
+        <v>2.019950693764346</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.02583536850494222</v>
+        <v>-0.02532879265190414</v>
       </c>
       <c r="W52">
-        <v>0.2418919798934654</v>
+        <v>0.241772529307319</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5578,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.1291768425247111</v>
+        <v>-0.1266439632595207</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5586,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.193884373867821</v>
+        <v>0.195784373867821</v>
       </c>
       <c r="C53">
-        <v>-158.9811916902526</v>
+        <v>-171.2331365735071</v>
       </c>
       <c r="D53">
-        <v>265.7048083097474</v>
+        <v>262.3388634264929</v>
       </c>
       <c r="E53">
-        <v>253.186</v>
+        <v>262.072</v>
       </c>
       <c r="F53">
-        <v>453.186</v>
+        <v>462.072</v>
       </c>
       <c r="G53">
         <v>28.5</v>
@@ -5622,37 +5633,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M53">
-        <v>106.8612588</v>
+        <v>108.9565776</v>
       </c>
       <c r="N53">
-        <v>-120.3945921333333</v>
+        <v>-122.4899109333333</v>
       </c>
       <c r="O53">
-        <v>-24.07891842666667</v>
+        <v>-24.49798218666667</v>
       </c>
       <c r="P53">
-        <v>-96.31567370666667</v>
+        <v>-97.99192874666667</v>
       </c>
       <c r="Q53">
-        <v>-52.11567370666667</v>
+        <v>-53.79192874666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1440415998389558</v>
+        <v>0.1460882998356007</v>
       </c>
       <c r="T53">
-        <v>2.019950693764346</v>
+        <v>2.062032999884436</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.02532879265190414</v>
+        <v>-0.02484170048552137</v>
       </c>
       <c r="W53">
-        <v>0.241772529307319</v>
+        <v>0.241657672974486</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5660,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.1266439632595207</v>
+        <v>-0.1242085024276067</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5668,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.195784373867821</v>
+        <v>0.197684373867821</v>
       </c>
       <c r="C54">
-        <v>-171.2331365735071</v>
+        <v>-183.400868774241</v>
       </c>
       <c r="D54">
-        <v>262.3388634264929</v>
+        <v>259.0571312257591</v>
       </c>
       <c r="E54">
-        <v>262.072</v>
+        <v>270.958</v>
       </c>
       <c r="F54">
-        <v>462.072</v>
+        <v>470.958</v>
       </c>
       <c r="G54">
         <v>28.5</v>
@@ -5704,37 +5715,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M54">
-        <v>108.9565776</v>
+        <v>111.0518964</v>
       </c>
       <c r="N54">
-        <v>-122.4899109333333</v>
+        <v>-124.5852297333333</v>
       </c>
       <c r="O54">
-        <v>-24.49798218666667</v>
+        <v>-24.91704594666667</v>
       </c>
       <c r="P54">
-        <v>-97.99192874666667</v>
+        <v>-99.66818378666667</v>
       </c>
       <c r="Q54">
-        <v>-53.79192874666667</v>
+        <v>-55.46818378666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1460882998356007</v>
+        <v>0.1482220934491241</v>
       </c>
       <c r="T54">
-        <v>2.062032999884436</v>
+        <v>2.105906042435169</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.02484170048552137</v>
+        <v>-0.02437298915560587</v>
       </c>
       <c r="W54">
-        <v>0.241657672974486</v>
+        <v>0.2415471508428919</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5742,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.1242085024276067</v>
+        <v>-0.1218649457780294</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5750,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.197684373867821</v>
+        <v>0.199584373867821</v>
       </c>
       <c r="C55">
-        <v>-183.400868774241</v>
+        <v>-195.4875096257751</v>
       </c>
       <c r="D55">
-        <v>259.0571312257591</v>
+        <v>255.8564903742249</v>
       </c>
       <c r="E55">
-        <v>270.958</v>
+        <v>279.8440000000001</v>
       </c>
       <c r="F55">
-        <v>470.958</v>
+        <v>479.8440000000001</v>
       </c>
       <c r="G55">
         <v>28.5</v>
@@ -5786,37 +5797,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M55">
-        <v>111.0518964</v>
+        <v>113.1472152</v>
       </c>
       <c r="N55">
-        <v>-124.5852297333333</v>
+        <v>-126.6805485333334</v>
       </c>
       <c r="O55">
-        <v>-24.91704594666667</v>
+        <v>-25.33610970666667</v>
       </c>
       <c r="P55">
-        <v>-99.66818378666667</v>
+        <v>-101.3444388266667</v>
       </c>
       <c r="Q55">
-        <v>-55.46818378666667</v>
+        <v>-57.14443882666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1482220934491241</v>
+        <v>0.1504486606980181</v>
       </c>
       <c r="T55">
-        <v>2.105906042435169</v>
+        <v>2.151686608575064</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.02437298915560587</v>
+        <v>-0.02392163750457613</v>
       </c>
       <c r="W55">
-        <v>0.2415471508428919</v>
+        <v>0.2414407221235791</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5824,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.1218649457780294</v>
+        <v>-0.1196081875228807</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5832,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.199584373867821</v>
+        <v>0.201484373867821</v>
       </c>
       <c r="C56">
-        <v>-195.4875096257751</v>
+        <v>-207.4960280881853</v>
       </c>
       <c r="D56">
-        <v>255.8564903742249</v>
+        <v>252.7339719118148</v>
       </c>
       <c r="E56">
-        <v>279.8440000000001</v>
+        <v>288.7300000000001</v>
       </c>
       <c r="F56">
-        <v>479.8440000000001</v>
+        <v>488.7300000000001</v>
       </c>
       <c r="G56">
         <v>28.5</v>
@@ -5868,37 +5879,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M56">
-        <v>113.1472152</v>
+        <v>115.242534</v>
       </c>
       <c r="N56">
-        <v>-126.6805485333334</v>
+        <v>-128.7758673333334</v>
       </c>
       <c r="O56">
-        <v>-25.33610970666667</v>
+        <v>-25.75517346666668</v>
       </c>
       <c r="P56">
-        <v>-101.3444388266667</v>
+        <v>-103.0206938666667</v>
       </c>
       <c r="Q56">
-        <v>-57.14443882666667</v>
+        <v>-58.82069386666669</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1504486606980181</v>
+        <v>0.1527741864913074</v>
       </c>
       <c r="T56">
-        <v>2.151686608575064</v>
+        <v>2.199501866543399</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.02392163750457613</v>
+        <v>-0.02348669864085657</v>
       </c>
       <c r="W56">
-        <v>0.2414407221235791</v>
+        <v>0.241338163539514</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5906,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.1196081875228807</v>
+        <v>-0.1174334932042829</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5914,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.201484373867821</v>
+        <v>0.203384373867821</v>
       </c>
       <c r="C57">
-        <v>-207.4960280881853</v>
+        <v>-219.4292499341483</v>
       </c>
       <c r="D57">
-        <v>252.7339719118148</v>
+        <v>249.6867500658517</v>
       </c>
       <c r="E57">
-        <v>288.7300000000001</v>
+        <v>297.616</v>
       </c>
       <c r="F57">
-        <v>488.7300000000001</v>
+        <v>497.616</v>
       </c>
       <c r="G57">
         <v>28.5</v>
@@ -5950,37 +5961,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M57">
-        <v>115.242534</v>
+        <v>117.3378528</v>
       </c>
       <c r="N57">
-        <v>-128.7758673333334</v>
+        <v>-130.8711861333334</v>
       </c>
       <c r="O57">
-        <v>-25.75517346666668</v>
+        <v>-26.17423722666668</v>
       </c>
       <c r="P57">
-        <v>-103.0206938666667</v>
+        <v>-104.6969489066667</v>
       </c>
       <c r="Q57">
-        <v>-58.82069386666669</v>
+        <v>-60.49694890666669</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1527741864913074</v>
+        <v>0.1552054180024734</v>
       </c>
       <c r="T57">
-        <v>2.199501866543399</v>
+        <v>2.249490545328476</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.02348669864085657</v>
+        <v>-0.02306729330798413</v>
       </c>
       <c r="W57">
-        <v>0.241338163539514</v>
+        <v>0.2412392677620226</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5988,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.1174334932042829</v>
+        <v>-0.1153364665399208</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5996,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.203384373867821</v>
+        <v>0.2052843738678211</v>
       </c>
       <c r="C58">
-        <v>-219.4292499341483</v>
+        <v>-231.2898662781815</v>
       </c>
       <c r="D58">
-        <v>249.6867500658517</v>
+        <v>246.7121337218185</v>
       </c>
       <c r="E58">
-        <v>297.616</v>
+        <v>306.5020000000001</v>
       </c>
       <c r="F58">
-        <v>497.616</v>
+        <v>506.5020000000001</v>
       </c>
       <c r="G58">
         <v>28.5</v>
@@ -6032,37 +6043,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M58">
-        <v>117.3378528</v>
+        <v>119.4331716</v>
       </c>
       <c r="N58">
-        <v>-130.8711861333334</v>
+        <v>-132.9665049333334</v>
       </c>
       <c r="O58">
-        <v>-26.17423722666668</v>
+        <v>-26.59330098666668</v>
       </c>
       <c r="P58">
-        <v>-104.6969489066667</v>
+        <v>-106.3732039466667</v>
       </c>
       <c r="Q58">
-        <v>-60.49694890666669</v>
+        <v>-62.17320394666669</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1552054180024734</v>
+        <v>0.1577497300490426</v>
       </c>
       <c r="T58">
-        <v>2.249490545328476</v>
+        <v>2.301804278940767</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.02306729330798413</v>
+        <v>-0.02266260395170371</v>
       </c>
       <c r="W58">
-        <v>0.2412392677620226</v>
+        <v>0.2411438420118117</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6070,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.1153364665399208</v>
+        <v>-0.1133130197585186</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6078,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2052843738678211</v>
+        <v>0.207184373867821</v>
       </c>
       <c r="C59">
-        <v>-231.2898662781815</v>
+        <v>-243.080441503385</v>
       </c>
       <c r="D59">
-        <v>246.7121337218185</v>
+        <v>243.807558496615</v>
       </c>
       <c r="E59">
-        <v>306.5020000000001</v>
+        <v>315.388</v>
       </c>
       <c r="F59">
-        <v>506.5020000000001</v>
+        <v>515.388</v>
       </c>
       <c r="G59">
         <v>28.5</v>
@@ -6114,37 +6125,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M59">
-        <v>119.4331716</v>
+        <v>121.5284904</v>
       </c>
       <c r="N59">
-        <v>-132.9665049333334</v>
+        <v>-135.0618237333333</v>
       </c>
       <c r="O59">
-        <v>-26.59330098666668</v>
+        <v>-27.01236474666667</v>
       </c>
       <c r="P59">
-        <v>-106.3732039466667</v>
+        <v>-108.0494589866667</v>
       </c>
       <c r="Q59">
-        <v>-62.17320394666669</v>
+        <v>-63.84945898666668</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1577497300490426</v>
+        <v>0.1604151998121151</v>
       </c>
       <c r="T59">
-        <v>2.301804278940767</v>
+        <v>2.35660914272507</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.02266260395170371</v>
+        <v>-0.02227186940081227</v>
       </c>
       <c r="W59">
-        <v>0.2411438420118117</v>
+        <v>0.2410517068047115</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6152,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.1133130197585186</v>
+        <v>-0.1113593470040612</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6160,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.207184373867821</v>
+        <v>0.209084373867821</v>
       </c>
       <c r="C60">
-        <v>-243.080441503385</v>
+        <v>-254.8034206347656</v>
       </c>
       <c r="D60">
-        <v>243.8075584966151</v>
+        <v>240.9705793652344</v>
       </c>
       <c r="E60">
-        <v>315.388</v>
+        <v>324.274</v>
       </c>
       <c r="F60">
-        <v>515.388</v>
+        <v>524.274</v>
       </c>
       <c r="G60">
         <v>28.5</v>
@@ -6196,37 +6207,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M60">
-        <v>121.5284904</v>
+        <v>123.6238092</v>
       </c>
       <c r="N60">
-        <v>-135.0618237333333</v>
+        <v>-137.1571425333333</v>
       </c>
       <c r="O60">
-        <v>-27.01236474666667</v>
+        <v>-27.43142850666667</v>
       </c>
       <c r="P60">
-        <v>-108.0494589866667</v>
+        <v>-109.7257140266667</v>
       </c>
       <c r="Q60">
-        <v>-63.84945898666668</v>
+        <v>-65.52571402666668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.160415199812115</v>
+        <v>0.1632106924904593</v>
       </c>
       <c r="T60">
-        <v>2.356609142725069</v>
+        <v>2.414087414498852</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.02227186940081227</v>
+        <v>-0.02189438008893409</v>
       </c>
       <c r="W60">
-        <v>0.2410517068047115</v>
+        <v>0.2409626948249707</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6234,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.1113593470040612</v>
+        <v>-0.1094719004446705</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6242,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.209084373867821</v>
+        <v>0.210984373867821</v>
       </c>
       <c r="C61">
-        <v>-254.8034206347656</v>
+        <v>-266.461136203699</v>
       </c>
       <c r="D61">
-        <v>240.9705793652344</v>
+        <v>238.198863796301</v>
       </c>
       <c r="E61">
-        <v>324.274</v>
+        <v>333.16</v>
       </c>
       <c r="F61">
-        <v>524.274</v>
+        <v>533.16</v>
       </c>
       <c r="G61">
         <v>28.5</v>
@@ -6278,37 +6289,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M61">
-        <v>123.6238092</v>
+        <v>125.719128</v>
       </c>
       <c r="N61">
-        <v>-137.1571425333333</v>
+        <v>-139.2524613333333</v>
       </c>
       <c r="O61">
-        <v>-27.43142850666667</v>
+        <v>-27.85049226666667</v>
       </c>
       <c r="P61">
-        <v>-109.7257140266667</v>
+        <v>-111.4019690666667</v>
       </c>
       <c r="Q61">
-        <v>-65.52571402666668</v>
+        <v>-67.20196906666668</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1632106924904593</v>
+        <v>0.1661459598027208</v>
       </c>
       <c r="T61">
-        <v>2.414087414498852</v>
+        <v>2.474439599861323</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.02189438008893409</v>
+        <v>-0.02152947375411852</v>
       </c>
       <c r="W61">
-        <v>0.2409626948249707</v>
+        <v>0.2408766499112212</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6316,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.1094719004446705</v>
+        <v>-0.1076473687705928</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6324,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.210984373867821</v>
+        <v>0.212884373867821</v>
       </c>
       <c r="C62">
-        <v>-266.461136203699</v>
+        <v>-278.055814644036</v>
       </c>
       <c r="D62">
-        <v>238.198863796301</v>
+        <v>235.490185355964</v>
       </c>
       <c r="E62">
-        <v>333.16</v>
+        <v>342.046</v>
       </c>
       <c r="F62">
-        <v>533.16</v>
+        <v>542.046</v>
       </c>
       <c r="G62">
         <v>28.5</v>
@@ -6360,37 +6371,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M62">
-        <v>125.719128</v>
+        <v>127.8144468</v>
       </c>
       <c r="N62">
-        <v>-139.2524613333333</v>
+        <v>-141.3477801333333</v>
       </c>
       <c r="O62">
-        <v>-27.85049226666667</v>
+        <v>-28.26955602666667</v>
       </c>
       <c r="P62">
-        <v>-111.4019690666667</v>
+        <v>-113.0782241066667</v>
       </c>
       <c r="Q62">
-        <v>-67.20196906666668</v>
+        <v>-68.87822410666668</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1661459598027208</v>
+        <v>0.1692317536438162</v>
       </c>
       <c r="T62">
-        <v>2.474439599861323</v>
+        <v>2.537886769088537</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.02152947375411852</v>
+        <v>-0.02117653156142806</v>
       </c>
       <c r="W62">
-        <v>0.2408766499112212</v>
+        <v>0.2407934261421847</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6398,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.1076473687705928</v>
+        <v>-0.1058826578071401</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6406,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.212884373867821</v>
+        <v>0.214784373867821</v>
       </c>
       <c r="C63">
-        <v>-278.055814644036</v>
+        <v>-289.5895822567167</v>
       </c>
       <c r="D63">
-        <v>235.490185355964</v>
+        <v>232.8424177432833</v>
       </c>
       <c r="E63">
-        <v>342.046</v>
+        <v>350.932</v>
       </c>
       <c r="F63">
-        <v>542.046</v>
+        <v>550.932</v>
       </c>
       <c r="G63">
         <v>28.5</v>
@@ -6442,37 +6453,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M63">
-        <v>127.8144468</v>
+        <v>129.9097656</v>
       </c>
       <c r="N63">
-        <v>-141.3477801333333</v>
+        <v>-143.4430989333333</v>
       </c>
       <c r="O63">
-        <v>-28.26955602666667</v>
+        <v>-28.68861978666667</v>
       </c>
       <c r="P63">
-        <v>-113.0782241066667</v>
+        <v>-114.7544791466667</v>
       </c>
       <c r="Q63">
-        <v>-68.87822410666668</v>
+        <v>-70.55447914666668</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1692317536438162</v>
+        <v>0.1724799576870745</v>
       </c>
       <c r="T63">
-        <v>2.537886769088537</v>
+        <v>2.604673263011919</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.02117653156142806</v>
+        <v>-0.02083497460075986</v>
       </c>
       <c r="W63">
-        <v>0.2407934261421847</v>
+        <v>0.2407128870108592</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6480,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.1058826578071401</v>
+        <v>-0.1041748730037992</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6488,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.214784373867821</v>
+        <v>0.216684373867821</v>
       </c>
       <c r="C64">
-        <v>-289.5895822567167</v>
+        <v>-301.0644707764735</v>
       </c>
       <c r="D64">
-        <v>232.8424177432833</v>
+        <v>230.2535292235265</v>
       </c>
       <c r="E64">
-        <v>350.932</v>
+        <v>359.818</v>
       </c>
       <c r="F64">
-        <v>550.932</v>
+        <v>559.818</v>
       </c>
       <c r="G64">
         <v>28.5</v>
@@ -6524,37 +6535,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M64">
-        <v>129.9097656</v>
+        <v>132.0050844</v>
       </c>
       <c r="N64">
-        <v>-143.4430989333333</v>
+        <v>-145.5384177333333</v>
       </c>
       <c r="O64">
-        <v>-28.68861978666667</v>
+        <v>-29.10768354666667</v>
       </c>
       <c r="P64">
-        <v>-114.7544791466667</v>
+        <v>-116.4307341866667</v>
       </c>
       <c r="Q64">
-        <v>-70.55447914666668</v>
+        <v>-72.23073418666668</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1724799576870745</v>
+        <v>0.1759037403272657</v>
       </c>
       <c r="T64">
-        <v>2.604673263011919</v>
+        <v>2.675069837687917</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.02083497460075986</v>
+        <v>-0.02050426071820811</v>
       </c>
       <c r="W64">
-        <v>0.2407128870108592</v>
+        <v>0.2406349046773535</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6562,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.1041748730037992</v>
+        <v>-0.1025213035910406</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6570,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.216684373867821</v>
+        <v>0.218584373867821</v>
       </c>
       <c r="C65">
-        <v>-301.0644707764735</v>
+        <v>-312.4824225712542</v>
       </c>
       <c r="D65">
-        <v>230.2535292235265</v>
+        <v>227.7215774287458</v>
       </c>
       <c r="E65">
-        <v>359.818</v>
+        <v>368.7040000000001</v>
       </c>
       <c r="F65">
-        <v>559.818</v>
+        <v>568.7040000000001</v>
       </c>
       <c r="G65">
         <v>28.5</v>
@@ -6606,37 +6617,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M65">
-        <v>132.0050844</v>
+        <v>134.1004032</v>
       </c>
       <c r="N65">
-        <v>-145.5384177333333</v>
+        <v>-147.6337365333333</v>
       </c>
       <c r="O65">
-        <v>-29.10768354666667</v>
+        <v>-29.52674730666667</v>
       </c>
       <c r="P65">
-        <v>-116.4307341866667</v>
+        <v>-118.1069892266667</v>
       </c>
       <c r="Q65">
-        <v>-72.23073418666668</v>
+        <v>-73.90698922666668</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1759037403272657</v>
+        <v>0.1795177331141342</v>
       </c>
       <c r="T65">
-        <v>2.675069837687917</v>
+        <v>2.749377333179248</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.02050426071820811</v>
+        <v>-0.02018388164448611</v>
       </c>
       <c r="W65">
-        <v>0.2406349046773535</v>
+        <v>0.2405593592917698</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6644,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.1025213035910406</v>
+        <v>-0.1009194082224305</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6652,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.218584373867821</v>
+        <v>0.220484373867821</v>
       </c>
       <c r="C66">
-        <v>-312.4824225712542</v>
+        <v>-323.8452955023271</v>
       </c>
       <c r="D66">
-        <v>227.7215774287458</v>
+        <v>225.2447044976729</v>
       </c>
       <c r="E66">
-        <v>368.7040000000001</v>
+        <v>377.59</v>
       </c>
       <c r="F66">
-        <v>568.7040000000001</v>
+        <v>577.59</v>
       </c>
       <c r="G66">
         <v>28.5</v>
@@ -6688,37 +6699,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M66">
-        <v>134.1004032</v>
+        <v>136.195722</v>
       </c>
       <c r="N66">
-        <v>-147.6337365333333</v>
+        <v>-149.7290553333333</v>
       </c>
       <c r="O66">
-        <v>-29.52674730666667</v>
+        <v>-29.94581106666667</v>
       </c>
       <c r="P66">
-        <v>-118.1069892266667</v>
+        <v>-119.7832442666667</v>
       </c>
       <c r="Q66">
-        <v>-73.90698922666668</v>
+        <v>-75.58324426666668</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1795177331141342</v>
+        <v>0.1833382397745381</v>
       </c>
       <c r="T66">
-        <v>2.749377333179248</v>
+        <v>2.827930971270084</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.02018388164448611</v>
+        <v>-0.0198733603884171</v>
       </c>
       <c r="W66">
-        <v>0.2405593592917698</v>
+        <v>0.2404861383795888</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6726,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.1009194082224305</v>
+        <v>-0.09936680194208547</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6734,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.220484373867821</v>
+        <v>0.222384373867821</v>
       </c>
       <c r="C67">
-        <v>-323.8452955023271</v>
+        <v>-335.1548674706255</v>
       </c>
       <c r="D67">
-        <v>225.2447044976729</v>
+        <v>222.8211325293745</v>
       </c>
       <c r="E67">
-        <v>377.59</v>
+        <v>386.476</v>
       </c>
       <c r="F67">
-        <v>577.59</v>
+        <v>586.476</v>
       </c>
       <c r="G67">
         <v>28.5</v>
@@ -6770,37 +6781,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M67">
-        <v>136.195722</v>
+        <v>138.2910408</v>
       </c>
       <c r="N67">
-        <v>-149.7290553333333</v>
+        <v>-151.8243741333334</v>
       </c>
       <c r="O67">
-        <v>-29.94581106666667</v>
+        <v>-30.36487482666667</v>
       </c>
       <c r="P67">
-        <v>-119.7832442666667</v>
+        <v>-121.4594993066667</v>
       </c>
       <c r="Q67">
-        <v>-75.58324426666668</v>
+        <v>-77.25949930666668</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1833382397745381</v>
+        <v>0.187383482120848</v>
       </c>
       <c r="T67">
-        <v>2.827930971270084</v>
+        <v>2.911105411601556</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.0198733603884171</v>
+        <v>-0.01957224886738047</v>
       </c>
       <c r="W67">
-        <v>0.2404861383795888</v>
+        <v>0.2404151362829283</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6808,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.09936680194208547</v>
+        <v>-0.09786124433690224</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6816,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.222384373867821</v>
+        <v>0.224284373867821</v>
       </c>
       <c r="C68">
-        <v>-335.1548674706255</v>
+        <v>-346.4128406727129</v>
       </c>
       <c r="D68">
-        <v>222.8211325293745</v>
+        <v>220.4491593272871</v>
       </c>
       <c r="E68">
-        <v>386.476</v>
+        <v>395.3620000000001</v>
       </c>
       <c r="F68">
-        <v>586.476</v>
+        <v>595.3620000000001</v>
       </c>
       <c r="G68">
         <v>28.5</v>
@@ -6852,37 +6863,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M68">
-        <v>138.2910408</v>
+        <v>140.3863596</v>
       </c>
       <c r="N68">
-        <v>-151.8243741333334</v>
+        <v>-153.9196929333334</v>
       </c>
       <c r="O68">
-        <v>-30.36487482666667</v>
+        <v>-30.78393858666667</v>
       </c>
       <c r="P68">
-        <v>-121.4594993066667</v>
+        <v>-123.1357543466667</v>
       </c>
       <c r="Q68">
-        <v>-77.25949930666668</v>
+        <v>-78.93575434666668</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.187383482120848</v>
+        <v>0.1916738906699646</v>
       </c>
       <c r="T68">
-        <v>2.911105411601556</v>
+        <v>2.999320727104635</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.01957224886738047</v>
+        <v>-0.01928012574995688</v>
       </c>
       <c r="W68">
-        <v>0.2404151362829283</v>
+        <v>0.2403462536518398</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6890,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.09786124433690224</v>
+        <v>-0.09640062874978428</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6898,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.224284373867821</v>
+        <v>0.226184373867821</v>
       </c>
       <c r="C69">
-        <v>-346.4128406727129</v>
+        <v>-357.6208455877771</v>
       </c>
       <c r="D69">
-        <v>220.4491593272871</v>
+        <v>218.1271544122229</v>
       </c>
       <c r="E69">
-        <v>395.3620000000001</v>
+        <v>404.248</v>
       </c>
       <c r="F69">
-        <v>595.3620000000001</v>
+        <v>604.248</v>
       </c>
       <c r="G69">
         <v>28.5</v>
@@ -6934,37 +6945,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M69">
-        <v>140.3863596</v>
+        <v>142.4816784</v>
       </c>
       <c r="N69">
-        <v>-153.9196929333334</v>
+        <v>-156.0150117333334</v>
       </c>
       <c r="O69">
-        <v>-30.78393858666667</v>
+        <v>-31.20300234666667</v>
       </c>
       <c r="P69">
-        <v>-123.1357543466667</v>
+        <v>-124.8120093866667</v>
       </c>
       <c r="Q69">
-        <v>-78.93575434666668</v>
+        <v>-80.61200938666668</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1916738906699646</v>
+        <v>0.196232449753401</v>
       </c>
       <c r="T69">
-        <v>2.999320727104635</v>
+        <v>3.093049499826655</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.01928012574995688</v>
+        <v>-0.0189965944889281</v>
       </c>
       <c r="W69">
-        <v>0.2403462536518398</v>
+        <v>0.2402793969804893</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6972,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.09640062874978428</v>
+        <v>-0.09498297244464049</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6980,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.226184373867821</v>
+        <v>0.228084373867821</v>
       </c>
       <c r="C70">
-        <v>-357.6208455877771</v>
+        <v>-368.7804447152796</v>
       </c>
       <c r="D70">
-        <v>218.1271544122229</v>
+        <v>215.8535552847204</v>
       </c>
       <c r="E70">
-        <v>404.248</v>
+        <v>413.134</v>
       </c>
       <c r="F70">
-        <v>604.248</v>
+        <v>613.134</v>
       </c>
       <c r="G70">
         <v>28.5</v>
@@ -7016,37 +7027,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M70">
-        <v>142.4816784</v>
+        <v>144.5769972</v>
       </c>
       <c r="N70">
-        <v>-156.0150117333334</v>
+        <v>-158.1103305333334</v>
       </c>
       <c r="O70">
-        <v>-31.20300234666667</v>
+        <v>-31.62206610666667</v>
       </c>
       <c r="P70">
-        <v>-124.8120093866667</v>
+        <v>-126.4882644266667</v>
       </c>
       <c r="Q70">
-        <v>-80.61200938666668</v>
+        <v>-82.28826442666669</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.196232449753401</v>
+        <v>0.2010851094228656</v>
       </c>
       <c r="T70">
-        <v>3.093049499826655</v>
+        <v>3.192825290143643</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.0189965944889281</v>
+        <v>-0.01872128152532045</v>
       </c>
       <c r="W70">
-        <v>0.2402793969804893</v>
+        <v>0.2402144781836706</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7054,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.09498297244464049</v>
+        <v>-0.09360640762660233</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7062,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.228084373867821</v>
+        <v>0.2299843738678211</v>
       </c>
       <c r="C71">
-        <v>-368.7804447152796</v>
+        <v>-379.8931360812654</v>
       </c>
       <c r="D71">
-        <v>215.8535552847204</v>
+        <v>213.6268639187346</v>
       </c>
       <c r="E71">
-        <v>413.134</v>
+        <v>422.0200000000001</v>
       </c>
       <c r="F71">
-        <v>613.134</v>
+        <v>622.0200000000001</v>
       </c>
       <c r="G71">
         <v>28.5</v>
@@ -7098,37 +7109,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M71">
-        <v>144.5769972</v>
+        <v>146.672316</v>
       </c>
       <c r="N71">
-        <v>-158.1103305333334</v>
+        <v>-160.2056493333334</v>
       </c>
       <c r="O71">
-        <v>-31.62206610666667</v>
+        <v>-32.04112986666667</v>
       </c>
       <c r="P71">
-        <v>-126.4882644266667</v>
+        <v>-128.1645194666667</v>
       </c>
       <c r="Q71">
-        <v>-82.28826442666669</v>
+        <v>-83.96451946666669</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2010851094228656</v>
+        <v>0.2062612797369611</v>
       </c>
       <c r="T71">
-        <v>3.192825290143643</v>
+        <v>3.299252799815099</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.01872128152532045</v>
+        <v>-0.0184538346463873</v>
       </c>
       <c r="W71">
-        <v>0.2402144781836706</v>
+        <v>0.2401514142096182</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7136,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.09360640762660233</v>
+        <v>-0.09226917323193651</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7144,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2299843738678211</v>
+        <v>0.231884373867821</v>
       </c>
       <c r="C72">
-        <v>-379.8931360812654</v>
+        <v>-390.9603565298663</v>
       </c>
       <c r="D72">
-        <v>213.6268639187346</v>
+        <v>211.4456434701338</v>
       </c>
       <c r="E72">
-        <v>422.0200000000001</v>
+        <v>430.9060000000001</v>
       </c>
       <c r="F72">
-        <v>622.0200000000001</v>
+        <v>630.9060000000001</v>
       </c>
       <c r="G72">
         <v>28.5</v>
@@ -7180,37 +7191,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M72">
-        <v>146.672316</v>
+        <v>148.7676348</v>
       </c>
       <c r="N72">
-        <v>-160.2056493333334</v>
+        <v>-162.3009681333334</v>
       </c>
       <c r="O72">
-        <v>-32.04112986666667</v>
+        <v>-32.46019362666667</v>
       </c>
       <c r="P72">
-        <v>-128.1645194666667</v>
+        <v>-129.8407745066667</v>
       </c>
       <c r="Q72">
-        <v>-83.96451946666669</v>
+        <v>-85.64077450666669</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2062612797369611</v>
+        <v>0.2117944273140977</v>
       </c>
       <c r="T72">
-        <v>3.299252799815099</v>
+        <v>3.413020137739757</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.0184538346463873</v>
+        <v>-0.01819392148235368</v>
       </c>
       <c r="W72">
-        <v>0.2401514142096182</v>
+        <v>0.240090126685539</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7218,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.09226917323193651</v>
+        <v>-0.09096960741176829</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7226,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.231884373867821</v>
+        <v>0.233784373867821</v>
       </c>
       <c r="C73">
-        <v>-390.9603565298661</v>
+        <v>-401.9834848151978</v>
       </c>
       <c r="D73">
-        <v>211.4456434701338</v>
+        <v>209.3085151848022</v>
       </c>
       <c r="E73">
-        <v>430.9059999999999</v>
+        <v>439.792</v>
       </c>
       <c r="F73">
-        <v>630.9059999999999</v>
+        <v>639.792</v>
       </c>
       <c r="G73">
         <v>28.5</v>
@@ -7262,37 +7273,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M73">
-        <v>148.7676348</v>
+        <v>150.8629536</v>
       </c>
       <c r="N73">
-        <v>-162.3009681333333</v>
+        <v>-164.3962869333334</v>
       </c>
       <c r="O73">
-        <v>-32.46019362666667</v>
+        <v>-32.87925738666667</v>
       </c>
       <c r="P73">
-        <v>-129.8407745066667</v>
+        <v>-131.5170295466667</v>
       </c>
       <c r="Q73">
-        <v>-85.64077450666666</v>
+        <v>-87.31702954666669</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2117944273140976</v>
+        <v>0.2177227997181725</v>
       </c>
       <c r="T73">
-        <v>3.413020137739756</v>
+        <v>3.534913714087605</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.01819392148235368</v>
+        <v>-0.0179412281284321</v>
       </c>
       <c r="W73">
-        <v>0.240090126685539</v>
+        <v>0.2400305415926843</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7300,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.09096960741176829</v>
+        <v>-0.08970614064216043</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7308,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.233784373867821</v>
+        <v>0.235684373867821</v>
       </c>
       <c r="C74">
-        <v>-401.9834848151978</v>
+        <v>-412.963844507628</v>
       </c>
       <c r="D74">
-        <v>209.3085151848022</v>
+        <v>207.214155492372</v>
       </c>
       <c r="E74">
-        <v>439.792</v>
+        <v>448.678</v>
       </c>
       <c r="F74">
-        <v>639.792</v>
+        <v>648.678</v>
       </c>
       <c r="G74">
         <v>28.5</v>
@@ -7344,37 +7355,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M74">
-        <v>150.8629536</v>
+        <v>152.9582724</v>
       </c>
       <c r="N74">
-        <v>-164.3962869333334</v>
+        <v>-166.4916057333333</v>
       </c>
       <c r="O74">
-        <v>-32.87925738666667</v>
+        <v>-33.29832114666667</v>
       </c>
       <c r="P74">
-        <v>-131.5170295466667</v>
+        <v>-133.1932845866667</v>
       </c>
       <c r="Q74">
-        <v>-87.31702954666669</v>
+        <v>-88.99328458666666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2177227997181725</v>
+        <v>0.2240903108188456</v>
       </c>
       <c r="T74">
-        <v>3.534913714087605</v>
+        <v>3.665836444238997</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.0179412281284321</v>
+        <v>-0.01769545788009742</v>
       </c>
       <c r="W74">
-        <v>0.2400305415926843</v>
+        <v>0.239972588968127</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7382,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.08970614064216043</v>
+        <v>-0.08847728940048705</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7390,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.235684373867821</v>
+        <v>0.237584373867821</v>
       </c>
       <c r="C75">
-        <v>-412.963844507628</v>
+        <v>-423.9027067272938</v>
       </c>
       <c r="D75">
-        <v>207.214155492372</v>
+        <v>205.1612932727062</v>
       </c>
       <c r="E75">
-        <v>448.678</v>
+        <v>457.564</v>
       </c>
       <c r="F75">
-        <v>648.678</v>
+        <v>657.564</v>
       </c>
       <c r="G75">
         <v>28.5</v>
@@ -7426,37 +7437,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M75">
-        <v>152.9582724</v>
+        <v>155.0535912</v>
       </c>
       <c r="N75">
-        <v>-166.4916057333333</v>
+        <v>-168.5869245333333</v>
       </c>
       <c r="O75">
-        <v>-33.29832114666667</v>
+        <v>-33.71738490666667</v>
       </c>
       <c r="P75">
-        <v>-133.1932845866667</v>
+        <v>-134.8695396266667</v>
       </c>
       <c r="Q75">
-        <v>-88.99328458666666</v>
+        <v>-90.66953962666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2240903108188456</v>
+        <v>0.2309476304657243</v>
       </c>
       <c r="T75">
-        <v>3.665836444238997</v>
+        <v>3.806830153632805</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.01769545788009742</v>
+        <v>-0.01745633007090691</v>
       </c>
       <c r="W75">
-        <v>0.239972588968127</v>
+        <v>0.2399162026307199</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7464,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.08847728940048705</v>
+        <v>-0.08728165035453461</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7472,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.237584373867821</v>
+        <v>0.239484373867821</v>
       </c>
       <c r="C76">
-        <v>-423.9027067272938</v>
+        <v>-434.8012927167251</v>
       </c>
       <c r="D76">
-        <v>205.1612932727062</v>
+        <v>203.1487072832749</v>
       </c>
       <c r="E76">
-        <v>457.564</v>
+        <v>466.45</v>
       </c>
       <c r="F76">
-        <v>657.564</v>
+        <v>666.45</v>
       </c>
       <c r="G76">
         <v>28.5</v>
@@ -7508,37 +7519,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M76">
-        <v>155.0535912</v>
+        <v>157.14891</v>
       </c>
       <c r="N76">
-        <v>-168.5869245333333</v>
+        <v>-170.6822433333334</v>
       </c>
       <c r="O76">
-        <v>-33.71738490666667</v>
+        <v>-34.13644866666667</v>
       </c>
       <c r="P76">
-        <v>-134.8695396266667</v>
+        <v>-136.5457946666667</v>
       </c>
       <c r="Q76">
-        <v>-90.66953962666666</v>
+        <v>-92.34579466666669</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2309476304657243</v>
+        <v>0.2383535356843533</v>
       </c>
       <c r="T76">
-        <v>3.806830153632805</v>
+        <v>3.959103359778118</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.01745633007090691</v>
+        <v>-0.01722357900329482</v>
       </c>
       <c r="W76">
-        <v>0.2399162026307199</v>
+        <v>0.2398613199289769</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7546,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.08728165035453461</v>
+        <v>-0.08611789501647404</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7554,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.239484373867821</v>
+        <v>0.241384373867821</v>
       </c>
       <c r="C77">
-        <v>-434.8012927167251</v>
+        <v>-445.6607762635194</v>
       </c>
       <c r="D77">
-        <v>203.1487072832749</v>
+        <v>201.1752237364806</v>
       </c>
       <c r="E77">
-        <v>466.45</v>
+        <v>475.336</v>
       </c>
       <c r="F77">
-        <v>666.45</v>
+        <v>675.336</v>
       </c>
       <c r="G77">
         <v>28.5</v>
@@ -7590,37 +7601,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M77">
-        <v>157.14891</v>
+        <v>159.2442288</v>
       </c>
       <c r="N77">
-        <v>-170.6822433333334</v>
+        <v>-172.7775621333333</v>
       </c>
       <c r="O77">
-        <v>-34.13644866666667</v>
+        <v>-34.55551242666667</v>
       </c>
       <c r="P77">
-        <v>-136.5457946666667</v>
+        <v>-138.2220497066667</v>
       </c>
       <c r="Q77">
-        <v>-92.34579466666669</v>
+        <v>-94.02204970666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2383535356843533</v>
+        <v>0.2463765996712013</v>
       </c>
       <c r="T77">
-        <v>3.959103359778118</v>
+        <v>4.124065999768872</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.01722357900329482</v>
+        <v>-0.01699695296377778</v>
       </c>
       <c r="W77">
-        <v>0.2398613199289769</v>
+        <v>0.2398078815088588</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7628,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.08611789501647404</v>
+        <v>-0.08498476481888884</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7636,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.241384373867821</v>
+        <v>0.243284373867821</v>
       </c>
       <c r="C78">
-        <v>-445.6607762635194</v>
+        <v>-456.4822859831651</v>
       </c>
       <c r="D78">
-        <v>201.1752237364806</v>
+        <v>199.2397140168349</v>
       </c>
       <c r="E78">
-        <v>475.336</v>
+        <v>484.222</v>
       </c>
       <c r="F78">
-        <v>675.336</v>
+        <v>684.222</v>
       </c>
       <c r="G78">
         <v>28.5</v>
@@ -7672,37 +7683,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M78">
-        <v>159.2442288</v>
+        <v>161.3395476</v>
       </c>
       <c r="N78">
-        <v>-172.7775621333333</v>
+        <v>-174.8728809333333</v>
       </c>
       <c r="O78">
-        <v>-34.55551242666667</v>
+        <v>-34.97457618666667</v>
       </c>
       <c r="P78">
-        <v>-138.2220497066667</v>
+        <v>-139.8983047466667</v>
       </c>
       <c r="Q78">
-        <v>-94.02204970666666</v>
+        <v>-95.69830474666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2463765996712013</v>
+        <v>0.2550973213960362</v>
       </c>
       <c r="T78">
-        <v>4.124065999768872</v>
+        <v>4.303373217150129</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.01699695296377778</v>
+        <v>-0.01677621331489755</v>
       </c>
       <c r="W78">
-        <v>0.2398078815088588</v>
+        <v>0.2397558310996529</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7710,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.08498476481888884</v>
+        <v>-0.08388106657448779</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7718,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.243284373867821</v>
+        <v>0.245184373867821</v>
       </c>
       <c r="C79">
-        <v>-456.4822859831651</v>
+        <v>-467.2669074713413</v>
       </c>
       <c r="D79">
-        <v>199.2397140168349</v>
+        <v>197.3410925286588</v>
       </c>
       <c r="E79">
-        <v>484.222</v>
+        <v>493.1080000000001</v>
       </c>
       <c r="F79">
-        <v>684.222</v>
+        <v>693.1080000000001</v>
       </c>
       <c r="G79">
         <v>28.5</v>
@@ -7754,37 +7765,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M79">
-        <v>161.3395476</v>
+        <v>163.4348664</v>
       </c>
       <c r="N79">
-        <v>-174.8728809333333</v>
+        <v>-176.9681997333334</v>
       </c>
       <c r="O79">
-        <v>-34.97457618666667</v>
+        <v>-35.39363994666667</v>
       </c>
       <c r="P79">
-        <v>-139.8983047466667</v>
+        <v>-141.5745597866667</v>
       </c>
       <c r="Q79">
-        <v>-95.69830474666666</v>
+        <v>-97.37455978666669</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2550973213960362</v>
+        <v>0.2646108360049469</v>
       </c>
       <c r="T79">
-        <v>4.303373217150129</v>
+        <v>4.498981090656952</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.01677621331489755</v>
+        <v>-0.01656113365701424</v>
       </c>
       <c r="W79">
-        <v>0.2397558310996529</v>
+        <v>0.239705115316324</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7792,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.08388106657448779</v>
+        <v>-0.0828056682850713</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7800,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.245184373867821</v>
+        <v>0.247084373867821</v>
       </c>
       <c r="C80">
-        <v>-467.2669074713413</v>
+        <v>-478.0156853343197</v>
       </c>
       <c r="D80">
-        <v>197.3410925286588</v>
+        <v>195.4783146656803</v>
       </c>
       <c r="E80">
-        <v>493.1080000000001</v>
+        <v>501.994</v>
       </c>
       <c r="F80">
-        <v>693.1080000000001</v>
+        <v>701.994</v>
       </c>
       <c r="G80">
         <v>28.5</v>
@@ -7836,37 +7847,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M80">
-        <v>163.4348664</v>
+        <v>165.5301852</v>
       </c>
       <c r="N80">
-        <v>-176.9681997333334</v>
+        <v>-179.0635185333333</v>
       </c>
       <c r="O80">
-        <v>-35.39363994666667</v>
+        <v>-35.81270370666667</v>
       </c>
       <c r="P80">
-        <v>-141.5745597866667</v>
+        <v>-143.2508148266667</v>
       </c>
       <c r="Q80">
-        <v>-97.37455978666669</v>
+        <v>-99.05081482666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2646108360049469</v>
+        <v>0.2750303996242301</v>
       </c>
       <c r="T80">
-        <v>4.498981090656952</v>
+        <v>4.71321828545014</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.01656113365701424</v>
+        <v>-0.0163514990537609</v>
       </c>
       <c r="W80">
-        <v>0.239705115316324</v>
+        <v>0.2396556834768769</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7874,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.0828056682850713</v>
+        <v>-0.08175749526880449</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7882,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.247084373867821</v>
+        <v>0.248984373867821</v>
       </c>
       <c r="C81">
-        <v>-478.0156853343197</v>
+        <v>-488.7296251054481</v>
       </c>
       <c r="D81">
-        <v>195.4783146656803</v>
+        <v>193.650374894552</v>
       </c>
       <c r="E81">
-        <v>501.994</v>
+        <v>510.8800000000001</v>
       </c>
       <c r="F81">
-        <v>701.994</v>
+        <v>710.8800000000001</v>
       </c>
       <c r="G81">
         <v>28.5</v>
@@ -7918,37 +7929,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M81">
-        <v>165.5301852</v>
+        <v>167.625504</v>
       </c>
       <c r="N81">
-        <v>-179.0635185333333</v>
+        <v>-181.1588373333334</v>
       </c>
       <c r="O81">
-        <v>-35.81270370666667</v>
+        <v>-36.23176746666667</v>
       </c>
       <c r="P81">
-        <v>-143.2508148266667</v>
+        <v>-144.9270698666667</v>
       </c>
       <c r="Q81">
-        <v>-99.05081482666667</v>
+        <v>-100.7270698666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2750303996242301</v>
+        <v>0.2864919196054416</v>
       </c>
       <c r="T81">
-        <v>4.71321828545014</v>
+        <v>4.948879199722647</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.0163514990537609</v>
+        <v>-0.01614710531558889</v>
       </c>
       <c r="W81">
-        <v>0.2396556834768769</v>
+        <v>0.2396074874334159</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.08175749526880449</v>
+        <v>-0.08073552657794436</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7964,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.248984373867821</v>
+        <v>0.250884373867821</v>
       </c>
       <c r="C82">
-        <v>-488.7296251054481</v>
+        <v>-499.4096950551011</v>
       </c>
       <c r="D82">
-        <v>193.650374894552</v>
+        <v>191.856304944899</v>
       </c>
       <c r="E82">
-        <v>510.8800000000001</v>
+        <v>519.7660000000001</v>
       </c>
       <c r="F82">
-        <v>710.8800000000001</v>
+        <v>719.7660000000001</v>
       </c>
       <c r="G82">
         <v>28.5</v>
@@ -8000,37 +8011,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M82">
-        <v>167.625504</v>
+        <v>169.7208228</v>
       </c>
       <c r="N82">
-        <v>-181.1588373333334</v>
+        <v>-183.2541561333334</v>
       </c>
       <c r="O82">
-        <v>-36.23176746666667</v>
+        <v>-36.65083122666667</v>
       </c>
       <c r="P82">
-        <v>-144.9270698666667</v>
+        <v>-146.6033249066667</v>
       </c>
       <c r="Q82">
-        <v>-100.7270698666667</v>
+        <v>-102.4033249066667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2864919196054416</v>
+        <v>0.2991599153741491</v>
       </c>
       <c r="T82">
-        <v>4.948879199722647</v>
+        <v>5.20934652602384</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.01614710531558889</v>
+        <v>-0.01594775833638409</v>
       </c>
       <c r="W82">
-        <v>0.2396074874334159</v>
+        <v>0.2395604814157194</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8038,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.08073552657794436</v>
+        <v>-0.07973879168192033</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8046,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.250884373867821</v>
+        <v>0.252784373867821</v>
       </c>
       <c r="C83">
-        <v>-499.4096950551011</v>
+        <v>-510.0568279009461</v>
       </c>
       <c r="D83">
-        <v>191.856304944899</v>
+        <v>190.095172099054</v>
       </c>
       <c r="E83">
-        <v>519.7660000000001</v>
+        <v>528.652</v>
       </c>
       <c r="F83">
-        <v>719.7660000000001</v>
+        <v>728.652</v>
       </c>
       <c r="G83">
         <v>28.5</v>
@@ -8082,37 +8093,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M83">
-        <v>169.7208228</v>
+        <v>171.8161416</v>
       </c>
       <c r="N83">
-        <v>-183.2541561333334</v>
+        <v>-185.3494749333333</v>
       </c>
       <c r="O83">
-        <v>-36.65083122666667</v>
+        <v>-37.06989498666667</v>
       </c>
       <c r="P83">
-        <v>-146.6033249066667</v>
+        <v>-148.2795799466667</v>
       </c>
       <c r="Q83">
-        <v>-102.4033249066667</v>
+        <v>-104.0795799466667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2991599153741491</v>
+        <v>0.3132354662282685</v>
       </c>
       <c r="T83">
-        <v>5.20934652602384</v>
+        <v>5.498754666358497</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.01594775833638409</v>
+        <v>-0.01575327347862331</v>
       </c>
       <c r="W83">
-        <v>0.2395604814157194</v>
+        <v>0.2395146218862594</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8120,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.07973879168192033</v>
+        <v>-0.07876636739311649</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8128,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.252784373867821</v>
+        <v>0.254684373867821</v>
       </c>
       <c r="C84">
-        <v>-510.0568279009461</v>
+        <v>-520.6719224248704</v>
       </c>
       <c r="D84">
-        <v>190.095172099054</v>
+        <v>188.3660775751297</v>
       </c>
       <c r="E84">
-        <v>528.652</v>
+        <v>537.5380000000001</v>
       </c>
       <c r="F84">
-        <v>728.652</v>
+        <v>737.5380000000001</v>
       </c>
       <c r="G84">
         <v>28.5</v>
@@ -8164,37 +8175,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M84">
-        <v>171.8161416</v>
+        <v>173.9114604</v>
       </c>
       <c r="N84">
-        <v>-185.3494749333333</v>
+        <v>-187.4447937333334</v>
       </c>
       <c r="O84">
-        <v>-37.06989498666667</v>
+        <v>-37.48895874666668</v>
       </c>
       <c r="P84">
-        <v>-148.2795799466667</v>
+        <v>-149.9558349866667</v>
       </c>
       <c r="Q84">
-        <v>-104.0795799466667</v>
+        <v>-105.7558349866667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3132354662282685</v>
+        <v>0.3289669642416961</v>
       </c>
       <c r="T84">
-        <v>5.498754666358497</v>
+        <v>5.822210823203116</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.01575327347862331</v>
+        <v>-0.01556347500297724</v>
       </c>
       <c r="W84">
-        <v>0.2395146218862594</v>
+        <v>0.239469867405702</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8202,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.07876636739311649</v>
+        <v>-0.07781737501488628</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8210,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.254684373867821</v>
+        <v>0.256584373867821</v>
       </c>
       <c r="C85">
-        <v>-520.6719224248704</v>
+        <v>-531.2558450024576</v>
       </c>
       <c r="D85">
-        <v>188.3660775751297</v>
+        <v>186.6681549975425</v>
       </c>
       <c r="E85">
-        <v>537.5380000000001</v>
+        <v>546.4240000000001</v>
       </c>
       <c r="F85">
-        <v>737.5380000000001</v>
+        <v>746.4240000000001</v>
       </c>
       <c r="G85">
         <v>28.5</v>
@@ -8246,37 +8257,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M85">
-        <v>173.9114604</v>
+        <v>176.0067792</v>
       </c>
       <c r="N85">
-        <v>-187.4447937333334</v>
+        <v>-189.5401125333334</v>
       </c>
       <c r="O85">
-        <v>-37.48895874666668</v>
+        <v>-37.90802250666668</v>
       </c>
       <c r="P85">
-        <v>-149.9558349866667</v>
+        <v>-151.6320900266667</v>
       </c>
       <c r="Q85">
-        <v>-105.7558349866667</v>
+        <v>-107.4320900266667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3289669642416961</v>
+        <v>0.3466648995068021</v>
       </c>
       <c r="T85">
-        <v>5.822210823203116</v>
+        <v>6.186098999653312</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.01556347500297724</v>
+        <v>-0.01537819553865608</v>
       </c>
       <c r="W85">
-        <v>0.239469867405702</v>
+        <v>0.2394261785080151</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8284,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.07781737501488628</v>
+        <v>-0.07689097769328046</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8292,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.256584373867821</v>
+        <v>0.258484373867821</v>
       </c>
       <c r="C86">
-        <v>-531.2558450024575</v>
+        <v>-541.8094310504845</v>
       </c>
       <c r="D86">
-        <v>186.6681549975425</v>
+        <v>185.0005689495155</v>
       </c>
       <c r="E86">
-        <v>546.424</v>
+        <v>555.3099999999999</v>
       </c>
       <c r="F86">
-        <v>746.424</v>
+        <v>755.3099999999999</v>
       </c>
       <c r="G86">
         <v>28.5</v>
@@ -8328,37 +8339,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M86">
-        <v>176.0067792</v>
+        <v>178.102098</v>
       </c>
       <c r="N86">
-        <v>-189.5401125333333</v>
+        <v>-191.6354313333333</v>
       </c>
       <c r="O86">
-        <v>-37.90802250666667</v>
+        <v>-38.32708626666666</v>
       </c>
       <c r="P86">
-        <v>-151.6320900266667</v>
+        <v>-153.3083450666666</v>
       </c>
       <c r="Q86">
-        <v>-107.4320900266667</v>
+        <v>-109.1083450666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.346664899506802</v>
+        <v>0.3667225594739221</v>
       </c>
       <c r="T86">
-        <v>6.186098999653308</v>
+        <v>6.598505599630195</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.01537819553865609</v>
+        <v>-0.01519727559114249</v>
       </c>
       <c r="W86">
-        <v>0.2394261785080151</v>
+        <v>0.2393835175843914</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8366,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.07689097769328046</v>
+        <v>-0.07598637795571239</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8374,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.258484373867821</v>
+        <v>0.260384373867821</v>
       </c>
       <c r="C87">
-        <v>-541.8094310504845</v>
+        <v>-552.3334863975183</v>
       </c>
       <c r="D87">
-        <v>185.0005689495155</v>
+        <v>183.3625136024817</v>
       </c>
       <c r="E87">
-        <v>555.3099999999999</v>
+        <v>564.196</v>
       </c>
       <c r="F87">
-        <v>755.3099999999999</v>
+        <v>764.196</v>
       </c>
       <c r="G87">
         <v>28.5</v>
@@ -8410,37 +8421,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M87">
-        <v>178.102098</v>
+        <v>180.1974168</v>
       </c>
       <c r="N87">
-        <v>-191.6354313333333</v>
+        <v>-193.7307501333333</v>
       </c>
       <c r="O87">
-        <v>-38.32708626666666</v>
+        <v>-38.74615002666667</v>
       </c>
       <c r="P87">
-        <v>-153.3083450666666</v>
+        <v>-154.9846001066667</v>
       </c>
       <c r="Q87">
-        <v>-109.1083450666666</v>
+        <v>-110.7846001066667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3667225594739221</v>
+        <v>0.3896455994363451</v>
       </c>
       <c r="T87">
-        <v>6.598505599630195</v>
+        <v>7.06982742817521</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.01519727559114249</v>
+        <v>-0.01502056308426874</v>
       </c>
       <c r="W87">
-        <v>0.2393835175843914</v>
+        <v>0.2393418487752706</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8448,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.07598637795571239</v>
+        <v>-0.07510281542134356</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8456,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.260384373867821</v>
+        <v>0.262284373867821</v>
       </c>
       <c r="C88">
-        <v>-552.3334863975183</v>
+        <v>-562.8287885823374</v>
       </c>
       <c r="D88">
-        <v>183.3625136024817</v>
+        <v>181.7532114176625</v>
       </c>
       <c r="E88">
-        <v>564.196</v>
+        <v>573.082</v>
       </c>
       <c r="F88">
-        <v>764.196</v>
+        <v>773.082</v>
       </c>
       <c r="G88">
         <v>28.5</v>
@@ -8492,37 +8503,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M88">
-        <v>180.1974168</v>
+        <v>182.2927356</v>
       </c>
       <c r="N88">
-        <v>-193.7307501333333</v>
+        <v>-195.8260689333333</v>
       </c>
       <c r="O88">
-        <v>-38.74615002666667</v>
+        <v>-39.16521378666667</v>
       </c>
       <c r="P88">
-        <v>-154.9846001066667</v>
+        <v>-156.6608551466667</v>
       </c>
       <c r="Q88">
-        <v>-110.7846001066667</v>
+        <v>-112.4608551466667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3896455994363451</v>
+        <v>0.4160952609314485</v>
       </c>
       <c r="T88">
-        <v>7.06982742817521</v>
+        <v>7.613660307265609</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.01502056308426874</v>
+        <v>-0.01484791293387484</v>
       </c>
       <c r="W88">
-        <v>0.2393418487752706</v>
+        <v>0.2393011378698077</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8530,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.07510281542134356</v>
+        <v>-0.07423956466937409</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8538,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.262284373867821</v>
+        <v>0.264184373867821</v>
       </c>
       <c r="C89">
-        <v>-562.8287885823374</v>
+        <v>-573.2960880845748</v>
       </c>
       <c r="D89">
-        <v>181.7532114176625</v>
+        <v>180.1719119154253</v>
       </c>
       <c r="E89">
-        <v>573.082</v>
+        <v>581.9680000000001</v>
       </c>
       <c r="F89">
-        <v>773.082</v>
+        <v>781.9680000000001</v>
       </c>
       <c r="G89">
         <v>28.5</v>
@@ -8574,37 +8585,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M89">
-        <v>182.2927356</v>
+        <v>184.3880544</v>
       </c>
       <c r="N89">
-        <v>-195.8260689333333</v>
+        <v>-197.9213877333333</v>
       </c>
       <c r="O89">
-        <v>-39.16521378666667</v>
+        <v>-39.58427754666667</v>
       </c>
       <c r="P89">
-        <v>-156.6608551466667</v>
+        <v>-158.3371101866667</v>
       </c>
       <c r="Q89">
-        <v>-112.4608551466667</v>
+        <v>-114.1371101866667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4160952609314485</v>
+        <v>0.4469531993424027</v>
       </c>
       <c r="T89">
-        <v>7.613660307265609</v>
+        <v>8.248131999537746</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.01484791293387484</v>
+        <v>-0.01467918665053536</v>
       </c>
       <c r="W89">
-        <v>0.2393011378698077</v>
+        <v>0.2392613522121962</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8612,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.07423956466937409</v>
+        <v>-0.07339593325267679</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8620,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.264184373867821</v>
+        <v>0.266084373867821</v>
       </c>
       <c r="C90">
-        <v>-573.2960880845748</v>
+        <v>-583.7361094916706</v>
       </c>
       <c r="D90">
-        <v>180.1719119154253</v>
+        <v>178.6178905083295</v>
       </c>
       <c r="E90">
-        <v>581.9680000000001</v>
+        <v>590.854</v>
       </c>
       <c r="F90">
-        <v>781.9680000000001</v>
+        <v>790.854</v>
       </c>
       <c r="G90">
         <v>28.5</v>
@@ -8656,37 +8667,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M90">
-        <v>184.3880544</v>
+        <v>186.4833732</v>
       </c>
       <c r="N90">
-        <v>-197.9213877333333</v>
+        <v>-200.0167065333333</v>
       </c>
       <c r="O90">
-        <v>-39.58427754666667</v>
+        <v>-40.00334130666667</v>
       </c>
       <c r="P90">
-        <v>-158.3371101866667</v>
+        <v>-160.0133652266667</v>
       </c>
       <c r="Q90">
-        <v>-114.1371101866667</v>
+        <v>-115.8133652266667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4469531993424027</v>
+        <v>0.4834216720098938</v>
       </c>
       <c r="T90">
-        <v>8.248131999537746</v>
+        <v>8.997962181313904</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.01467918665053536</v>
+        <v>-0.01451425196906866</v>
       </c>
       <c r="W90">
-        <v>0.2392613522121962</v>
+        <v>0.2392224606143064</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8694,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.07339593325267679</v>
+        <v>-0.07257125984534341</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8702,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.266084373867821</v>
+        <v>0.267984373867821</v>
       </c>
       <c r="C91">
-        <v>-583.7361094916706</v>
+        <v>-594.1495526059543</v>
       </c>
       <c r="D91">
-        <v>178.6178905083295</v>
+        <v>177.0904473940457</v>
       </c>
       <c r="E91">
-        <v>590.854</v>
+        <v>599.74</v>
       </c>
       <c r="F91">
-        <v>790.854</v>
+        <v>799.74</v>
       </c>
       <c r="G91">
         <v>28.5</v>
@@ -8738,37 +8749,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M91">
-        <v>186.4833732</v>
+        <v>188.578692</v>
       </c>
       <c r="N91">
-        <v>-200.0167065333333</v>
+        <v>-202.1120253333333</v>
       </c>
       <c r="O91">
-        <v>-40.00334130666667</v>
+        <v>-40.42240506666667</v>
       </c>
       <c r="P91">
-        <v>-160.0133652266667</v>
+        <v>-161.6896202666667</v>
       </c>
       <c r="Q91">
-        <v>-115.8133652266667</v>
+        <v>-117.4896202666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4834216720098938</v>
+        <v>0.5271838392108832</v>
       </c>
       <c r="T91">
-        <v>8.997962181313904</v>
+        <v>9.897758399445296</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.01451425196906866</v>
+        <v>-0.01435298250274568</v>
       </c>
       <c r="W91">
-        <v>0.2392224606143064</v>
+        <v>0.2391844332741475</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8776,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.07257125984534341</v>
+        <v>-0.0717649125137283</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8784,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.267984373867821</v>
+        <v>0.269884373867821</v>
       </c>
       <c r="C92">
-        <v>-594.1495526059543</v>
+        <v>-604.5370934954015</v>
       </c>
       <c r="D92">
-        <v>177.0904473940457</v>
+        <v>175.5889065045987</v>
       </c>
       <c r="E92">
-        <v>599.74</v>
+        <v>608.6260000000001</v>
       </c>
       <c r="F92">
-        <v>799.74</v>
+        <v>808.6260000000001</v>
       </c>
       <c r="G92">
         <v>28.5</v>
@@ -8820,37 +8831,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M92">
-        <v>188.578692</v>
+        <v>190.6740108</v>
       </c>
       <c r="N92">
-        <v>-202.1120253333333</v>
+        <v>-204.2073441333334</v>
       </c>
       <c r="O92">
-        <v>-40.42240506666667</v>
+        <v>-40.84146882666667</v>
       </c>
       <c r="P92">
-        <v>-161.6896202666667</v>
+        <v>-163.3658753066667</v>
       </c>
       <c r="Q92">
-        <v>-117.4896202666667</v>
+        <v>-119.1658753066667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5271838392108832</v>
+        <v>0.5806709324565369</v>
       </c>
       <c r="T92">
-        <v>9.897758399445296</v>
+        <v>10.997509332717</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.01435298250274568</v>
+        <v>-0.01419525742029792</v>
       </c>
       <c r="W92">
-        <v>0.2391844332741475</v>
+        <v>0.2391472416997062</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8858,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.0717649125137283</v>
+        <v>-0.07097628710148962</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8866,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.269884373867821</v>
+        <v>0.271784373867821</v>
       </c>
       <c r="C93">
-        <v>-604.5370934954015</v>
+        <v>-614.8993854913863</v>
       </c>
       <c r="D93">
-        <v>175.5889065045987</v>
+        <v>174.1126145086137</v>
       </c>
       <c r="E93">
-        <v>608.6260000000001</v>
+        <v>617.5120000000001</v>
       </c>
       <c r="F93">
-        <v>808.6260000000001</v>
+        <v>817.5120000000001</v>
       </c>
       <c r="G93">
         <v>28.5</v>
@@ -8902,37 +8913,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M93">
-        <v>190.6740108</v>
+        <v>192.7693296</v>
       </c>
       <c r="N93">
-        <v>-204.2073441333334</v>
+        <v>-206.3026629333334</v>
       </c>
       <c r="O93">
-        <v>-40.84146882666667</v>
+        <v>-41.26053258666667</v>
       </c>
       <c r="P93">
-        <v>-163.3658753066667</v>
+        <v>-165.0421303466667</v>
       </c>
       <c r="Q93">
-        <v>-119.1658753066667</v>
+        <v>-120.8421303466667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5806709324565369</v>
+        <v>0.6475297990136041</v>
       </c>
       <c r="T93">
-        <v>10.997509332717</v>
+        <v>12.37219799930662</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.01419525742029792</v>
+        <v>-0.01404096114399034</v>
       </c>
       <c r="W93">
-        <v>0.2391472416997062</v>
+        <v>0.2391108586377529</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8940,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.07097628710148962</v>
+        <v>-0.07020480571995158</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8948,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.271784373867821</v>
+        <v>0.273684373867821</v>
       </c>
       <c r="C94">
-        <v>-614.8993854913863</v>
+        <v>-625.2370601365212</v>
       </c>
       <c r="D94">
-        <v>174.1126145086137</v>
+        <v>172.6609398634788</v>
       </c>
       <c r="E94">
-        <v>617.5120000000001</v>
+        <v>626.398</v>
       </c>
       <c r="F94">
-        <v>817.5120000000001</v>
+        <v>826.398</v>
       </c>
       <c r="G94">
         <v>28.5</v>
@@ -8984,37 +8995,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M94">
-        <v>192.7693296</v>
+        <v>194.8646484</v>
       </c>
       <c r="N94">
-        <v>-206.3026629333334</v>
+        <v>-208.3979817333334</v>
       </c>
       <c r="O94">
-        <v>-41.26053258666667</v>
+        <v>-41.67959634666667</v>
       </c>
       <c r="P94">
-        <v>-165.0421303466667</v>
+        <v>-166.7183853866667</v>
       </c>
       <c r="Q94">
-        <v>-120.8421303466667</v>
+        <v>-122.5183853866667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6475297990136041</v>
+        <v>0.7334911988726907</v>
       </c>
       <c r="T94">
-        <v>12.37219799930662</v>
+        <v>14.13965485635043</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.01404096114399034</v>
+        <v>-0.01388998306717324</v>
       </c>
       <c r="W94">
-        <v>0.2391108586377529</v>
+        <v>0.2390752580072395</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9022,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.07020480571995158</v>
+        <v>-0.06944991533586609</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9030,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.273684373867821</v>
+        <v>0.275584373867821</v>
       </c>
       <c r="C95">
-        <v>-625.2370601365212</v>
+        <v>-635.5507280854712</v>
       </c>
       <c r="D95">
-        <v>172.6609398634788</v>
+        <v>171.2332719145289</v>
       </c>
       <c r="E95">
-        <v>626.398</v>
+        <v>635.2840000000001</v>
       </c>
       <c r="F95">
-        <v>826.398</v>
+        <v>835.2840000000001</v>
       </c>
       <c r="G95">
         <v>28.5</v>
@@ -9066,37 +9077,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M95">
-        <v>194.8646484</v>
+        <v>196.9599672</v>
       </c>
       <c r="N95">
-        <v>-208.3979817333334</v>
+        <v>-210.4933005333334</v>
       </c>
       <c r="O95">
-        <v>-41.67959634666667</v>
+        <v>-42.09866010666667</v>
       </c>
       <c r="P95">
-        <v>-166.7183853866667</v>
+        <v>-168.3946404266667</v>
       </c>
       <c r="Q95">
-        <v>-122.5183853866667</v>
+        <v>-124.1946404266667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7334911988726907</v>
+        <v>0.848106398684806</v>
       </c>
       <c r="T95">
-        <v>14.13965485635043</v>
+        <v>16.49626399907551</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.01388998306717324</v>
+        <v>-0.01374221728986288</v>
       </c>
       <c r="W95">
-        <v>0.2390752580072395</v>
+        <v>0.2390404148369497</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9104,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.06944991533586609</v>
+        <v>-0.06871108644931434</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9112,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.275584373867821</v>
+        <v>0.277484373867821</v>
       </c>
       <c r="C96">
-        <v>-635.5507280854712</v>
+        <v>-645.8409799614446</v>
       </c>
       <c r="D96">
-        <v>171.2332719145289</v>
+        <v>169.8290200385554</v>
       </c>
       <c r="E96">
-        <v>635.2840000000001</v>
+        <v>644.1700000000001</v>
       </c>
       <c r="F96">
-        <v>835.2840000000001</v>
+        <v>844.1700000000001</v>
       </c>
       <c r="G96">
         <v>28.5</v>
@@ -9148,37 +9159,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M96">
-        <v>196.9599672</v>
+        <v>199.055286</v>
       </c>
       <c r="N96">
-        <v>-210.4933005333334</v>
+        <v>-212.5886193333334</v>
       </c>
       <c r="O96">
-        <v>-42.09866010666667</v>
+        <v>-42.51772386666667</v>
       </c>
       <c r="P96">
-        <v>-168.3946404266667</v>
+        <v>-170.0708954666667</v>
       </c>
       <c r="Q96">
-        <v>-124.1946404266667</v>
+        <v>-125.8708954666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.848106398684806</v>
+        <v>1.008567678421768</v>
       </c>
       <c r="T96">
-        <v>16.49626399907551</v>
+        <v>19.79551679889062</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.01374221728986288</v>
+        <v>-0.01359756237102222</v>
       </c>
       <c r="W96">
-        <v>0.2390404148369497</v>
+        <v>0.2390063052070871</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9186,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.06871108644931434</v>
+        <v>-0.06798781185511116</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9194,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.277484373867821</v>
+        <v>0.279384373867821</v>
       </c>
       <c r="C97">
-        <v>-645.8409799614446</v>
+        <v>-656.1083871708834</v>
       </c>
       <c r="D97">
-        <v>169.8290200385554</v>
+        <v>168.4476128291167</v>
       </c>
       <c r="E97">
-        <v>644.1700000000001</v>
+        <v>653.056</v>
       </c>
       <c r="F97">
-        <v>844.1700000000001</v>
+        <v>853.056</v>
       </c>
       <c r="G97">
         <v>28.5</v>
@@ -9230,37 +9241,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M97">
-        <v>199.055286</v>
+        <v>201.1506048</v>
       </c>
       <c r="N97">
-        <v>-212.5886193333334</v>
+        <v>-214.6839381333334</v>
       </c>
       <c r="O97">
-        <v>-42.51772386666667</v>
+        <v>-42.93678762666667</v>
       </c>
       <c r="P97">
-        <v>-170.0708954666667</v>
+        <v>-171.7471505066667</v>
       </c>
       <c r="Q97">
-        <v>-125.8708954666667</v>
+        <v>-127.5471505066667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.008567678421768</v>
+        <v>1.24925959802721</v>
       </c>
       <c r="T97">
-        <v>19.79551679889062</v>
+        <v>24.74439599861328</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.01359756237102222</v>
+        <v>-0.01345592109632408</v>
       </c>
       <c r="W97">
-        <v>0.2390063052070871</v>
+        <v>0.2389729061945132</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9268,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.06798781185511116</v>
+        <v>-0.06727960548162026</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9276,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.279384373867821</v>
+        <v>0.281284373867821</v>
       </c>
       <c r="C98">
-        <v>-656.1083871708834</v>
+        <v>-666.3535026787131</v>
       </c>
       <c r="D98">
-        <v>168.4476128291167</v>
+        <v>167.088497321287</v>
       </c>
       <c r="E98">
-        <v>653.056</v>
+        <v>661.942</v>
       </c>
       <c r="F98">
-        <v>853.056</v>
+        <v>861.942</v>
       </c>
       <c r="G98">
         <v>28.5</v>
@@ -9312,37 +9323,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M98">
-        <v>201.1506048</v>
+        <v>203.2459236</v>
       </c>
       <c r="N98">
-        <v>-214.6839381333334</v>
+        <v>-216.7792569333333</v>
       </c>
       <c r="O98">
-        <v>-42.93678762666667</v>
+        <v>-43.35585138666667</v>
       </c>
       <c r="P98">
-        <v>-171.7471505066667</v>
+        <v>-173.4234055466667</v>
       </c>
       <c r="Q98">
-        <v>-127.5471505066667</v>
+        <v>-129.2234055466666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.249259598027207</v>
+        <v>1.650412797369609</v>
       </c>
       <c r="T98">
-        <v>24.74439599861321</v>
+        <v>32.99252799815095</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.01345592109632408</v>
+        <v>-0.0133172002602795</v>
       </c>
       <c r="W98">
-        <v>0.2389729061945132</v>
+        <v>0.2389401958213739</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9350,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.06727960548162026</v>
+        <v>-0.06658600130139747</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9358,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.281284373867821</v>
+        <v>0.283184373867821</v>
       </c>
       <c r="C99">
-        <v>-666.3535026787131</v>
+        <v>-676.5768617463625</v>
       </c>
       <c r="D99">
-        <v>167.088497321287</v>
+        <v>165.7511382536375</v>
       </c>
       <c r="E99">
-        <v>661.942</v>
+        <v>670.828</v>
       </c>
       <c r="F99">
-        <v>861.942</v>
+        <v>870.828</v>
       </c>
       <c r="G99">
         <v>28.5</v>
@@ -9394,37 +9405,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M99">
-        <v>203.2459236</v>
+        <v>205.3412424</v>
       </c>
       <c r="N99">
-        <v>-216.7792569333333</v>
+        <v>-218.8745757333333</v>
       </c>
       <c r="O99">
-        <v>-43.35585138666667</v>
+        <v>-43.77491514666667</v>
       </c>
       <c r="P99">
-        <v>-173.4234055466667</v>
+        <v>-175.0996605866667</v>
       </c>
       <c r="Q99">
-        <v>-129.2234055466666</v>
+        <v>-130.8996605866666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.650412797369609</v>
+        <v>2.452719196054413</v>
       </c>
       <c r="T99">
-        <v>32.99252799815095</v>
+        <v>49.48879199722642</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.0133172002602795</v>
+        <v>-0.01318131046170522</v>
       </c>
       <c r="W99">
-        <v>0.2389401958213739</v>
+        <v>0.2389081530068701</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9432,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.06658600130139747</v>
+        <v>-0.06590655230852605</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9440,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.283184373867821</v>
+        <v>0.285084373867821</v>
       </c>
       <c r="C100">
-        <v>-676.5768617463625</v>
+        <v>-686.7789826346237</v>
       </c>
       <c r="D100">
-        <v>165.7511382536375</v>
+        <v>164.4350173653763</v>
       </c>
       <c r="E100">
-        <v>670.828</v>
+        <v>679.7140000000001</v>
       </c>
       <c r="F100">
-        <v>870.828</v>
+        <v>879.7140000000001</v>
       </c>
       <c r="G100">
         <v>28.5</v>
@@ -9476,37 +9487,37 @@
         <v>-13.53333333333333</v>
       </c>
       <c r="M100">
-        <v>205.3412424</v>
+        <v>207.4365612</v>
       </c>
       <c r="N100">
-        <v>-218.8745757333333</v>
+        <v>-220.9698945333334</v>
       </c>
       <c r="O100">
-        <v>-43.77491514666667</v>
+        <v>-44.19397890666667</v>
       </c>
       <c r="P100">
-        <v>-175.0996605866667</v>
+        <v>-176.7759156266667</v>
       </c>
       <c r="Q100">
-        <v>-130.8996605866666</v>
+        <v>-132.5759156266667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.452719196054413</v>
+        <v>4.859638392108828</v>
       </c>
       <c r="T100">
-        <v>49.48879199722642</v>
+        <v>98.97758399445286</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.01318131046170522</v>
+        <v>-0.01304816591158698</v>
       </c>
       <c r="W100">
-        <v>0.2389081530068701</v>
+        <v>0.2388767575219523</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9514,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.06590655230852605</v>
+        <v>-0.06524082955793498</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.285084373867821</v>
-      </c>
-      <c r="C101">
-        <v>-686.7789826346237</v>
-      </c>
-      <c r="D101">
-        <v>164.4350173653763</v>
-      </c>
-      <c r="E101">
-        <v>679.7140000000001</v>
-      </c>
-      <c r="F101">
-        <v>879.7140000000001</v>
-      </c>
-      <c r="G101">
-        <v>28.5</v>
-      </c>
-      <c r="H101">
-        <v>688.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>30.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>44.2</v>
-      </c>
-      <c r="L101">
-        <v>-13.53333333333333</v>
-      </c>
-      <c r="M101">
-        <v>207.4365612</v>
-      </c>
-      <c r="N101">
-        <v>-220.9698945333334</v>
-      </c>
-      <c r="O101">
-        <v>-44.19397890666667</v>
-      </c>
-      <c r="P101">
-        <v>-176.7759156266667</v>
-      </c>
-      <c r="Q101">
-        <v>-132.5759156266667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.859638392108828</v>
-      </c>
-      <c r="T101">
-        <v>98.97758399445286</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.01304816591158698</v>
-      </c>
-      <c r="W101">
-        <v>0.2388767575219523</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.06524082955793498</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
